--- a/mainWidget/mainWidget/src/database/计算模型-跌落试验-45.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-跌落试验-45.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD0C5CF-5290-4AC1-8BC5-258C402C0672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F3D244-9C49-489C-B0F7-D091AFBECD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,9 +343,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -712,40 +715,40 @@
       <c r="C2" s="1">
         <v>8.8211999999999993</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="E2" s="1">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
         <v>-2.6200000000000001E-2</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="2">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="2">
         <v>-2.8999999999999998E-3</v>
       </c>
-      <c r="I2" s="1">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1">
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
         <v>-8.48E-2</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="2">
         <v>1.5E-3</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="2">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="2">
         <v>-9.5999999999999992E-3</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="2">
         <v>-0.13519999999999999</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="2">
         <v>1.34E-2</v>
       </c>
     </row>
@@ -759,40 +762,40 @@
       <c r="C3" s="1">
         <v>26.266200000000001</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>1E-3</v>
       </c>
-      <c r="E3" s="1">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
         <v>1.8800000000000001E-2</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="2">
         <v>-3.3999999999999998E-3</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="2">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="I3" s="1">
-        <v>0</v>
-      </c>
-      <c r="J3" s="1">
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
         <v>5.7299999999999997E-2</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K3" s="2">
         <v>-1.2999999999999999E-3</v>
       </c>
-      <c r="L3" s="1">
+      <c r="L3" s="2">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="M3" s="1">
+      <c r="M3" s="2">
         <v>-1.4500000000000001E-2</v>
       </c>
-      <c r="N3" s="1">
+      <c r="N3" s="2">
         <v>-0.1913</v>
       </c>
-      <c r="O3" s="1">
+      <c r="O3" s="2">
         <v>-2.0589</v>
       </c>
     </row>
@@ -806,40 +809,40 @@
       <c r="C4" s="1">
         <v>-25.203099999999999</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>7.1000000000000004E-3</v>
       </c>
-      <c r="E4" s="1">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
         <v>0.22270000000000001</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="2">
         <v>-5.33E-2</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="2">
         <v>4.6300000000000001E-2</v>
       </c>
-      <c r="I4" s="1">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1">
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
         <v>0.64959999999999996</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4" s="2">
         <v>3.9300000000000002E-2</v>
       </c>
-      <c r="L4" s="1">
+      <c r="L4" s="2">
         <v>5.4000000000000003E-3</v>
       </c>
-      <c r="M4" s="1">
+      <c r="M4" s="2">
         <v>0.17599999999999999</v>
       </c>
-      <c r="N4" s="1">
+      <c r="N4" s="2">
         <v>-1.6087</v>
       </c>
-      <c r="O4" s="1">
+      <c r="O4" s="2">
         <v>-13.3727</v>
       </c>
     </row>
@@ -853,40 +856,40 @@
       <c r="C5" s="1">
         <v>-2075.7078999999999</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>3.8899999999999997E-2</v>
       </c>
-      <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
         <v>-0.27929999999999999</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="2">
         <v>0.1024</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="2">
         <v>0.19800000000000001</v>
       </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
         <v>-3.6566000000000001</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K5" s="2">
         <v>-0.113</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L5" s="2">
         <v>4.1099999999999998E-2</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M5" s="2">
         <v>0.56310000000000004</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5" s="2">
         <v>4.2419000000000002</v>
       </c>
-      <c r="O5" s="1">
+      <c r="O5" s="2">
         <v>-40.209400000000002</v>
       </c>
     </row>
@@ -900,40 +903,40 @@
       <c r="C6" s="1">
         <v>-3930.1880999999998</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="2">
         <v>0.12570000000000001</v>
       </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
         <v>0.88900000000000001</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="2">
         <v>0.27</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="2">
         <v>0.55059999999999998</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
         <v>-9.8482000000000003</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6" s="2">
         <v>-0.13880000000000001</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L6" s="2">
         <v>0.1172</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M6" s="2">
         <v>1.0164</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6" s="2">
         <v>5.3682999999999996</v>
       </c>
-      <c r="O6" s="1">
+      <c r="O6" s="2">
         <v>-278.12110000000001</v>
       </c>
     </row>
@@ -947,40 +950,40 @@
       <c r="C7" s="1">
         <v>24.685600000000001</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="2">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
         <v>-3.3999999999999998E-3</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="2">
         <v>-2.3E-3</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="2">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
         <v>4.48E-2</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7" s="2">
         <v>1.8E-3</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7" s="2">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="M7" s="1">
+      <c r="M7" s="2">
         <v>-1.7500000000000002E-2</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7" s="2">
         <v>-0.16439999999999999</v>
       </c>
-      <c r="O7" s="1">
+      <c r="O7" s="2">
         <v>-2.2593999999999999</v>
       </c>
     </row>
@@ -994,40 +997,40 @@
       <c r="C8" s="1">
         <v>-0.46810000000000002</v>
       </c>
-      <c r="D8" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="D8" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="2">
         <v>-2.0000000000000001E-4</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="2">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1">
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K8" s="2">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="L8" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="M8" s="1">
+      <c r="L8" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="M8" s="2">
         <v>-2.9999999999999997E-4</v>
       </c>
-      <c r="N8" s="1">
+      <c r="N8" s="2">
         <v>-1.09E-2</v>
       </c>
-      <c r="O8" s="1">
+      <c r="O8" s="2">
         <v>1.2800000000000001E-2</v>
       </c>
     </row>
@@ -1041,40 +1044,40 @@
       <c r="C9" s="1">
         <v>-4.5602999999999998</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="2">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
         <v>-6.1000000000000004E-3</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="2">
         <v>-1.6000000000000001E-3</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="2">
         <v>1.9E-3</v>
       </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
         <v>3.1399999999999997E-2</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="2">
         <v>1.8E-3</v>
       </c>
-      <c r="L9" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="M9" s="1">
+      <c r="L9" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="M9" s="2">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="2">
         <v>-4.9200000000000001E-2</v>
       </c>
-      <c r="O9" s="1">
+      <c r="O9" s="2">
         <v>-0.1996</v>
       </c>
     </row>
@@ -1088,40 +1091,40 @@
       <c r="C10" s="1">
         <v>-20.006499999999999</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="2">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="E10" s="1">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="2">
         <v>-1.9E-3</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10" s="2">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
         <v>-0.1207</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K10" s="2">
         <v>-5.3E-3</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L10" s="2">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M10" s="2">
         <v>1.38E-2</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N10" s="2">
         <v>-0.1293</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O10" s="2">
         <v>1.2594000000000001</v>
       </c>
     </row>
@@ -1135,40 +1138,40 @@
       <c r="C11" s="1">
         <v>-7.1607000000000003</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="2">
         <v>2.35E-2</v>
       </c>
-      <c r="E11" s="1">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1">
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
         <v>-0.29310000000000003</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="2">
         <v>-7.9799999999999996E-2</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="2">
         <v>6.2899999999999998E-2</v>
       </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1">
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
         <v>-1.3003</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K11" s="2">
         <v>-3.85E-2</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L11" s="2">
         <v>1.6E-2</v>
       </c>
-      <c r="M11" s="1">
+      <c r="M11" s="2">
         <v>8.8400000000000006E-2</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N11" s="2">
         <v>-1.7969999999999999</v>
       </c>
-      <c r="O11" s="1">
+      <c r="O11" s="2">
         <v>-9.6062999999999992</v>
       </c>
     </row>
@@ -1182,40 +1185,40 @@
       <c r="C12" s="1">
         <v>32.298299999999998</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="2">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="E12" s="1">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1">
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
         <v>-2.07E-2</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="2">
         <v>-1.5E-3</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="2">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
         <v>-3.0999999999999999E-3</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12" s="2">
         <v>-6.9999999999999999E-4</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12" s="2">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="M12" s="1">
+      <c r="M12" s="2">
         <v>-1.6299999999999999E-2</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12" s="2">
         <v>-0.16270000000000001</v>
       </c>
-      <c r="O12" s="1">
+      <c r="O12" s="2">
         <v>-1.8993</v>
       </c>
     </row>
@@ -1229,40 +1232,40 @@
       <c r="C13" s="1">
         <v>-0.1636</v>
       </c>
-      <c r="D13" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0</v>
-      </c>
-      <c r="F13" s="1">
+      <c r="D13" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
         <v>1.5E-3</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="2">
         <v>-2.0000000000000001E-4</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="2">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="K13" s="1">
+      <c r="K13" s="2">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="L13" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="M13" s="1">
+      <c r="L13" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="M13" s="2">
         <v>-2.0000000000000001E-4</v>
       </c>
-      <c r="N13" s="1">
+      <c r="N13" s="2">
         <v>-1.3100000000000001E-2</v>
       </c>
-      <c r="O13" s="1">
+      <c r="O13" s="2">
         <v>-2.0000000000000001E-4</v>
       </c>
     </row>
@@ -1276,40 +1279,40 @@
       <c r="C14" s="1">
         <v>-4.6791999999999998</v>
       </c>
-      <c r="D14" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0</v>
-      </c>
-      <c r="F14" s="1">
+      <c r="D14" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
         <v>-1.1000000000000001E-3</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="2">
         <v>-1.2999999999999999E-3</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14" s="2">
         <v>1.4E-3</v>
       </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1">
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
         <v>3.7900000000000003E-2</v>
       </c>
-      <c r="K14" s="1">
+      <c r="K14" s="2">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="L14" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="M14" s="1">
+      <c r="L14" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="M14" s="2">
         <v>6.7999999999999996E-3</v>
       </c>
-      <c r="N14" s="1">
+      <c r="N14" s="2">
         <v>-3.4099999999999998E-2</v>
       </c>
-      <c r="O14" s="1">
+      <c r="O14" s="2">
         <v>7.6200000000000004E-2</v>
       </c>
     </row>
@@ -1323,40 +1326,40 @@
       <c r="C15" s="1">
         <v>4.7222999999999997</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="2">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="E15" s="1">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1">
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="2">
         <v>-2.3E-3</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1">
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
         <v>-1.84E-2</v>
       </c>
-      <c r="K15" s="1">
+      <c r="K15" s="2">
         <v>-1.1999999999999999E-3</v>
       </c>
-      <c r="L15" s="1">
+      <c r="L15" s="2">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="M15" s="1">
+      <c r="M15" s="2">
         <v>1.2E-2</v>
       </c>
-      <c r="N15" s="1">
+      <c r="N15" s="2">
         <v>-0.18240000000000001</v>
       </c>
-      <c r="O15" s="1">
+      <c r="O15" s="2">
         <v>-0.49819999999999998</v>
       </c>
     </row>
@@ -1370,40 +1373,40 @@
       <c r="C16" s="1">
         <v>116.9363</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="2">
         <v>1.7100000000000001E-2</v>
       </c>
-      <c r="E16" s="1">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1">
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
         <v>-7.6E-3</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="2">
         <v>-4.2500000000000003E-2</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="2">
         <v>5.2299999999999999E-2</v>
       </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1">
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
         <v>-0.999</v>
       </c>
-      <c r="K16" s="1">
+      <c r="K16" s="2">
         <v>-4.1000000000000002E-2</v>
       </c>
-      <c r="L16" s="1">
+      <c r="L16" s="2">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="M16" s="1">
+      <c r="M16" s="2">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="N16" s="1">
+      <c r="N16" s="2">
         <v>-1.6734</v>
       </c>
-      <c r="O16" s="1">
+      <c r="O16" s="2">
         <v>-17.1433</v>
       </c>
     </row>
@@ -1417,40 +1420,40 @@
       <c r="C17" s="1">
         <v>63.913400000000003</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="2">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="E17" s="1">
-        <v>0</v>
-      </c>
-      <c r="F17" s="1">
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
         <v>-4.24E-2</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="2">
         <v>-1.7500000000000002E-2</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17" s="2">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="I17" s="1">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
         <v>-0.15140000000000001</v>
       </c>
-      <c r="K17" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="L17" s="1">
+      <c r="K17" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="L17" s="2">
         <v>1.4E-3</v>
       </c>
-      <c r="M17" s="1">
+      <c r="M17" s="2">
         <v>-5.79E-2</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N17" s="2">
         <v>-8.6300000000000002E-2</v>
       </c>
-      <c r="O17" s="1">
+      <c r="O17" s="2">
         <v>-2.5954000000000002</v>
       </c>
     </row>
@@ -1464,40 +1467,40 @@
       <c r="C18" s="1">
         <v>1.1828000000000001</v>
       </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0</v>
-      </c>
-      <c r="F18" s="1">
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
         <v>-5.0000000000000001E-4</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="2">
         <v>-2.0000000000000001E-4</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18" s="2">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="I18" s="1">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1">
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="K18" s="1">
+      <c r="K18" s="2">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="L18" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="M18" s="1">
+      <c r="L18" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="M18" s="2">
         <v>-1.4E-3</v>
       </c>
-      <c r="N18" s="1">
+      <c r="N18" s="2">
         <v>-1.0999999999999999E-2</v>
       </c>
-      <c r="O18" s="1">
+      <c r="O18" s="2">
         <v>3.7900000000000003E-2</v>
       </c>
     </row>
@@ -1511,40 +1514,40 @@
       <c r="C19" s="1">
         <v>-3.8458000000000001</v>
       </c>
-      <c r="D19" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0</v>
-      </c>
-      <c r="F19" s="1">
+      <c r="D19" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="2">
         <v>-4.0000000000000002E-4</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19" s="2">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I19" s="1">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1">
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
         <v>1.29E-2</v>
       </c>
-      <c r="K19" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="L19" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="M19" s="1">
+      <c r="K19" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="L19" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="M19" s="2">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="N19" s="1">
+      <c r="N19" s="2">
         <v>-1.38E-2</v>
       </c>
-      <c r="O19" s="1">
+      <c r="O19" s="2">
         <v>0.35310000000000002</v>
       </c>
     </row>
@@ -1558,40 +1561,40 @@
       <c r="C20" s="1">
         <v>4.0095999999999998</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="2">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="E20" s="1">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1">
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
         <v>1.5E-3</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="2">
         <v>-2.2000000000000001E-3</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="2">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
-      <c r="J20" s="1">
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
         <v>1.9E-2</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20" s="2">
         <v>-1E-4</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L20" s="2">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="M20" s="1">
+      <c r="M20" s="2">
         <v>1.29E-2</v>
       </c>
-      <c r="N20" s="1">
+      <c r="N20" s="2">
         <v>-0.16250000000000001</v>
       </c>
-      <c r="O20" s="1">
+      <c r="O20" s="2">
         <v>-0.68130000000000002</v>
       </c>
     </row>
@@ -1605,40 +1608,40 @@
       <c r="C21" s="1">
         <v>-116.33499999999999</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="2">
         <v>2.35E-2</v>
       </c>
-      <c r="E21" s="1">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1">
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
         <v>-0.2989</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="2">
         <v>-7.3800000000000004E-2</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21" s="2">
         <v>6.6600000000000006E-2</v>
       </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1">
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
         <v>-2.2766999999999999</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K21" s="2">
         <v>-6.59E-2</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L21" s="2">
         <v>1.66E-2</v>
       </c>
-      <c r="M21" s="1">
+      <c r="M21" s="2">
         <v>8.1900000000000001E-2</v>
       </c>
-      <c r="N21" s="1">
+      <c r="N21" s="2">
         <v>-1.0645</v>
       </c>
-      <c r="O21" s="1">
+      <c r="O21" s="2">
         <v>-11.442299999999999</v>
       </c>
     </row>
@@ -1652,40 +1655,40 @@
       <c r="C22" s="1">
         <v>65.199799999999996</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="2">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="E22" s="1">
-        <v>0</v>
-      </c>
-      <c r="F22" s="1">
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
         <v>-6.7199999999999996E-2</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" s="2">
         <v>-1.95E-2</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="2">
         <v>6.7999999999999996E-3</v>
       </c>
-      <c r="I22" s="1">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1">
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
         <v>2.35E-2</v>
       </c>
-      <c r="K22" s="1">
+      <c r="K22" s="2">
         <v>-4.7000000000000002E-3</v>
       </c>
-      <c r="L22" s="1">
+      <c r="L22" s="2">
         <v>1.4E-3</v>
       </c>
-      <c r="M22" s="1">
+      <c r="M22" s="2">
         <v>-5.2999999999999999E-2</v>
       </c>
-      <c r="N22" s="1">
+      <c r="N22" s="2">
         <v>-0.1115</v>
       </c>
-      <c r="O22" s="1">
+      <c r="O22" s="2">
         <v>-1.7663</v>
       </c>
     </row>
@@ -1699,40 +1702,40 @@
       <c r="C23" s="1">
         <v>0.22389999999999999</v>
       </c>
-      <c r="D23" s="1">
-        <v>0</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1">
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2">
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1">
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
         <v>1.4200000000000001E-2</v>
       </c>
-      <c r="K23" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="L23" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="M23" s="1">
+      <c r="K23" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="L23" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="M23" s="2">
         <v>-5.0000000000000001E-4</v>
       </c>
-      <c r="N23" s="1">
+      <c r="N23" s="2">
         <v>-1.2800000000000001E-2</v>
       </c>
-      <c r="O23" s="1">
+      <c r="O23" s="2">
         <v>1.6899999999999998E-2</v>
       </c>
     </row>
@@ -1746,40 +1749,40 @@
       <c r="C24" s="1">
         <v>-2.1697000000000002</v>
       </c>
-      <c r="D24" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="E24" s="1">
-        <v>0</v>
-      </c>
-      <c r="F24" s="1">
+      <c r="D24" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
         <v>-3.5999999999999999E-3</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" s="2">
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24" s="2">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="I24" s="1">
-        <v>0</v>
-      </c>
-      <c r="J24" s="1">
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
         <v>6.7999999999999996E-3</v>
       </c>
-      <c r="K24" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="L24" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="M24" s="1">
+      <c r="K24" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="L24" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="M24" s="2">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="N24" s="1">
+      <c r="N24" s="2">
         <v>-3.15E-2</v>
       </c>
-      <c r="O24" s="1">
+      <c r="O24" s="2">
         <v>-2.5499999999999998E-2</v>
       </c>
     </row>
@@ -1793,40 +1796,40 @@
       <c r="C25" s="1">
         <v>-1.7814000000000001</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="2">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="E25" s="1">
-        <v>0</v>
-      </c>
-      <c r="F25" s="1">
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" s="2">
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25" s="2">
         <v>1.4E-3</v>
       </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
-      <c r="J25" s="1">
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="K25" s="1">
+      <c r="K25" s="2">
         <v>-4.0000000000000002E-4</v>
       </c>
-      <c r="L25" s="1">
+      <c r="L25" s="2">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="M25" s="1">
+      <c r="M25" s="2">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="N25" s="1">
+      <c r="N25" s="2">
         <v>-5.5599999999999997E-2</v>
       </c>
-      <c r="O25" s="1">
+      <c r="O25" s="2">
         <v>5.8099999999999999E-2</v>
       </c>
     </row>
@@ -1840,40 +1843,40 @@
       <c r="C26" s="1">
         <v>-90.206299999999999</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="2">
         <v>1.6799999999999999E-2</v>
       </c>
-      <c r="E26" s="1">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1">
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2">
         <v>-0.18149999999999999</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" s="2">
         <v>-6.2E-2</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H26" s="2">
         <v>4.41E-2</v>
       </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
-      <c r="J26" s="1">
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
         <v>-1.5721000000000001</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K26" s="2">
         <v>-5.28E-2</v>
       </c>
-      <c r="L26" s="1">
+      <c r="L26" s="2">
         <v>1.26E-2</v>
       </c>
-      <c r="M26" s="1">
+      <c r="M26" s="2">
         <v>7.17E-2</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N26" s="2">
         <v>-0.79459999999999997</v>
       </c>
-      <c r="O26" s="1">
+      <c r="O26" s="2">
         <v>-5.8758999999999997</v>
       </c>
     </row>
@@ -1887,40 +1890,40 @@
       <c r="C27" s="1">
         <v>23.620799999999999</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="2">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="E27" s="1">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1">
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="G27" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="H27" s="1">
+      <c r="G27" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="H27" s="2">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="I27" s="1">
-        <v>0</v>
-      </c>
-      <c r="J27" s="1">
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
         <v>0.13389999999999999</v>
       </c>
-      <c r="K27" s="1">
+      <c r="K27" s="2">
         <v>-3.5000000000000001E-3</v>
       </c>
-      <c r="L27" s="1">
+      <c r="L27" s="2">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="M27" s="1">
+      <c r="M27" s="2">
         <v>-1.04E-2</v>
       </c>
-      <c r="N27" s="1">
+      <c r="N27" s="2">
         <v>-0.183</v>
       </c>
-      <c r="O27" s="1">
+      <c r="O27" s="2">
         <v>-1.6662999999999999</v>
       </c>
     </row>
@@ -1934,40 +1937,40 @@
       <c r="C28" s="1">
         <v>-0.42949999999999999</v>
       </c>
-      <c r="D28" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1">
+      <c r="D28" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2">
         <v>-1.1000000000000001E-3</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28" s="2">
         <v>-1E-4</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H28" s="2">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="I28" s="1">
-        <v>0</v>
-      </c>
-      <c r="J28" s="1">
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="K28" s="1">
-        <v>0</v>
-      </c>
-      <c r="L28" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="M28" s="1">
+      <c r="K28" s="2">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="M28" s="2">
         <v>1E-3</v>
       </c>
-      <c r="N28" s="1">
+      <c r="N28" s="2">
         <v>-1.6E-2</v>
       </c>
-      <c r="O28" s="1">
+      <c r="O28" s="2">
         <v>6.1999999999999998E-3</v>
       </c>
     </row>
@@ -1981,40 +1984,40 @@
       <c r="C29" s="1">
         <v>-1.9615</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" s="2">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="E29" s="1">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1">
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
         <v>-7.1999999999999998E-3</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29" s="2">
         <v>-1.1999999999999999E-3</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H29" s="2">
         <v>1.5E-3</v>
       </c>
-      <c r="I29" s="1">
-        <v>0</v>
-      </c>
-      <c r="J29" s="1">
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2">
         <v>2.92E-2</v>
       </c>
-      <c r="K29" s="1">
+      <c r="K29" s="2">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="L29" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="M29" s="1">
+      <c r="L29" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="M29" s="2">
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="N29" s="1">
+      <c r="N29" s="2">
         <v>-5.3900000000000003E-2</v>
       </c>
-      <c r="O29" s="1">
+      <c r="O29" s="2">
         <v>-0.29549999999999998</v>
       </c>
     </row>
@@ -2028,40 +2031,40 @@
       <c r="C30" s="1">
         <v>-1.837</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" s="2">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="E30" s="1">
-        <v>0</v>
-      </c>
-      <c r="F30" s="1">
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2">
         <v>-4.7000000000000002E-3</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" s="2">
         <v>-8.9999999999999998E-4</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30" s="2">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="I30" s="1">
-        <v>0</v>
-      </c>
-      <c r="J30" s="1">
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2">
         <v>5.7500000000000002E-2</v>
       </c>
-      <c r="K30" s="1">
+      <c r="K30" s="2">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="L30" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="M30" s="1">
+      <c r="L30" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="M30" s="2">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N30" s="2">
         <v>-5.3499999999999999E-2</v>
       </c>
-      <c r="O30" s="1">
+      <c r="O30" s="2">
         <v>7.7999999999999996E-3</v>
       </c>
     </row>
@@ -2075,40 +2078,40 @@
       <c r="C31" s="1">
         <v>84.4529</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" s="2">
         <v>1.11E-2</v>
       </c>
-      <c r="E31" s="1">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1">
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2">
         <v>8.1900000000000001E-2</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G31" s="2">
         <v>-1.3299999999999999E-2</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31" s="2">
         <v>2.58E-2</v>
       </c>
-      <c r="I31" s="1">
-        <v>0</v>
-      </c>
-      <c r="J31" s="1">
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2">
         <v>-0.1037</v>
       </c>
-      <c r="K31" s="1">
+      <c r="K31" s="2">
         <v>-2.5899999999999999E-2</v>
       </c>
-      <c r="L31" s="1">
+      <c r="L31" s="2">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="M31" s="1">
+      <c r="M31" s="2">
         <v>5.9200000000000003E-2</v>
       </c>
-      <c r="N31" s="1">
+      <c r="N31" s="2">
         <v>-1.2926</v>
       </c>
-      <c r="O31" s="1">
+      <c r="O31" s="2">
         <v>-6.0380000000000003</v>
       </c>
     </row>
@@ -2122,40 +2125,40 @@
       <c r="C32" s="1">
         <v>19.222999999999999</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="2">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1">
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G32" s="2">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32" s="2">
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="I32" s="1">
-        <v>0</v>
-      </c>
-      <c r="J32" s="1">
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="K32" s="1">
+      <c r="K32" s="2">
         <v>-2.5000000000000001E-3</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L32" s="2">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="M32" s="1">
+      <c r="M32" s="2">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="N32" s="1">
+      <c r="N32" s="2">
         <v>-0.22289999999999999</v>
       </c>
-      <c r="O32" s="1">
+      <c r="O32" s="2">
         <v>-1.8352999999999999</v>
       </c>
     </row>
@@ -2169,40 +2172,40 @@
       <c r="C33" s="1">
         <v>-0.45939999999999998</v>
       </c>
-      <c r="D33" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="E33" s="1">
-        <v>0</v>
-      </c>
-      <c r="F33" s="1">
+      <c r="D33" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2">
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="G33" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="H33" s="1">
+      <c r="G33" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="H33" s="2">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="I33" s="1">
-        <v>0</v>
-      </c>
-      <c r="J33" s="1">
+      <c r="I33" s="2">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="K33" s="1">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="M33" s="1">
+      <c r="K33" s="2">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="M33" s="2">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N33" s="1">
+      <c r="N33" s="2">
         <v>-1.5299999999999999E-2</v>
       </c>
-      <c r="O33" s="1">
+      <c r="O33" s="2">
         <v>-2.3699999999999999E-2</v>
       </c>
     </row>
@@ -2216,40 +2219,40 @@
       <c r="C34" s="1">
         <v>-2.1200999999999999</v>
       </c>
-      <c r="D34" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="E34" s="1">
-        <v>0</v>
-      </c>
-      <c r="F34" s="1">
+      <c r="D34" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2">
         <v>-1.24E-2</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G34" s="2">
         <v>-1.6999999999999999E-3</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H34" s="2">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="I34" s="1">
-        <v>0</v>
-      </c>
-      <c r="J34" s="1">
+      <c r="I34" s="2">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="K34" s="1">
+      <c r="K34" s="2">
         <v>1.5E-3</v>
       </c>
-      <c r="L34" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="M34" s="1">
+      <c r="L34" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="M34" s="2">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="N34" s="1">
+      <c r="N34" s="2">
         <v>-7.4999999999999997E-2</v>
       </c>
-      <c r="O34" s="1">
+      <c r="O34" s="2">
         <v>-0.52610000000000001</v>
       </c>
     </row>
@@ -2263,40 +2266,40 @@
       <c r="C35" s="1">
         <v>-1.4162999999999999</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" s="2">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="E35" s="1">
-        <v>0</v>
-      </c>
-      <c r="F35" s="1">
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2">
         <v>-1.5E-3</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G35" s="2">
         <v>-8.0000000000000004E-4</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H35" s="2">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
-      <c r="J35" s="1">
+      <c r="I35" s="2">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2">
         <v>2.9700000000000001E-2</v>
       </c>
-      <c r="K35" s="1">
+      <c r="K35" s="2">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="L35" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="M35" s="1">
+      <c r="L35" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="M35" s="2">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="N35" s="1">
+      <c r="N35" s="2">
         <v>-3.8300000000000001E-2</v>
       </c>
-      <c r="O35" s="1">
+      <c r="O35" s="2">
         <v>-7.7399999999999997E-2</v>
       </c>
     </row>
@@ -2310,40 +2313,40 @@
       <c r="C36" s="1">
         <v>54.6312</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" s="2">
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="E36" s="1">
-        <v>0</v>
-      </c>
-      <c r="F36" s="1">
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G36" s="2">
         <v>-2.06E-2</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H36" s="2">
         <v>1.72E-2</v>
       </c>
-      <c r="I36" s="1">
-        <v>0</v>
-      </c>
-      <c r="J36" s="1">
+      <c r="I36" s="2">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2">
         <v>-3.8999999999999998E-3</v>
       </c>
-      <c r="K36" s="1">
+      <c r="K36" s="2">
         <v>-1.21E-2</v>
       </c>
-      <c r="L36" s="1">
+      <c r="L36" s="2">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="M36" s="1">
+      <c r="M36" s="2">
         <v>5.8400000000000001E-2</v>
       </c>
-      <c r="N36" s="1">
+      <c r="N36" s="2">
         <v>-1.1404000000000001</v>
       </c>
-      <c r="O36" s="1">
+      <c r="O36" s="2">
         <v>-3.5251999999999999</v>
       </c>
     </row>
@@ -2357,40 +2360,40 @@
       <c r="C37" s="1">
         <v>-9.3774999999999995</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" s="2">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="E37" s="1">
-        <v>0</v>
-      </c>
-      <c r="F37" s="1">
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2">
         <v>-1.4E-2</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G37" s="2">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="2">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="I37" s="1">
-        <v>0</v>
-      </c>
-      <c r="J37" s="1">
+      <c r="I37" s="2">
+        <v>0</v>
+      </c>
+      <c r="J37" s="2">
         <v>-0.14399999999999999</v>
       </c>
-      <c r="K37" s="1">
+      <c r="K37" s="2">
         <v>-1.1000000000000001E-3</v>
       </c>
-      <c r="L37" s="1">
+      <c r="L37" s="2">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="M37" s="1">
+      <c r="M37" s="2">
         <v>-3.3E-3</v>
       </c>
-      <c r="N37" s="1">
+      <c r="N37" s="2">
         <v>-0.15570000000000001</v>
       </c>
-      <c r="O37" s="1">
+      <c r="O37" s="2">
         <v>0.13869999999999999</v>
       </c>
     </row>
@@ -2404,40 +2407,40 @@
       <c r="C38" s="1">
         <v>8.0661000000000005</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" s="2">
         <v>2.8E-3</v>
       </c>
-      <c r="E38" s="1">
-        <v>0</v>
-      </c>
-      <c r="F38" s="1">
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2">
         <v>1.43E-2</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G38" s="2">
         <v>-8.0000000000000004E-4</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="2">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="I38" s="1">
-        <v>0</v>
-      </c>
-      <c r="J38" s="1">
+      <c r="I38" s="2">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2">
         <v>3.8600000000000002E-2</v>
       </c>
-      <c r="K38" s="1">
+      <c r="K38" s="2">
         <v>-8.9999999999999998E-4</v>
       </c>
-      <c r="L38" s="1">
+      <c r="L38" s="2">
         <v>1E-3</v>
       </c>
-      <c r="M38" s="1">
+      <c r="M38" s="2">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="N38" s="1">
+      <c r="N38" s="2">
         <v>-0.25369999999999998</v>
       </c>
-      <c r="O38" s="1">
+      <c r="O38" s="2">
         <v>-1.8654999999999999</v>
       </c>
     </row>
@@ -2451,40 +2454,40 @@
       <c r="C39" s="1">
         <v>-52.941099999999999</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" s="2">
         <v>1.01E-2</v>
       </c>
-      <c r="E39" s="1">
-        <v>0</v>
-      </c>
-      <c r="F39" s="1">
+      <c r="E39" s="2">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2">
         <v>0.14050000000000001</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G39" s="2">
         <v>-2.6100000000000002E-2</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H39" s="2">
         <v>4.9500000000000002E-2</v>
       </c>
-      <c r="I39" s="1">
-        <v>0</v>
-      </c>
-      <c r="J39" s="1">
+      <c r="I39" s="2">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2">
         <v>0.6855</v>
       </c>
-      <c r="K39" s="1">
+      <c r="K39" s="2">
         <v>3.1300000000000001E-2</v>
       </c>
-      <c r="L39" s="1">
+      <c r="L39" s="2">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="M39" s="1">
+      <c r="M39" s="2">
         <v>0.46079999999999999</v>
       </c>
-      <c r="N39" s="1">
+      <c r="N39" s="2">
         <v>-2.7578</v>
       </c>
-      <c r="O39" s="1">
+      <c r="O39" s="2">
         <v>-19.533200000000001</v>
       </c>
     </row>
@@ -2498,40 +2501,40 @@
       <c r="C40" s="1">
         <v>29.927399999999999</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" s="2">
         <v>1.24E-2</v>
       </c>
-      <c r="E40" s="1">
-        <v>0</v>
-      </c>
-      <c r="F40" s="1">
+      <c r="E40" s="2">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2">
         <v>0.12089999999999999</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G40" s="2">
         <v>-2.47E-2</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H40" s="2">
         <v>1.2800000000000001E-2</v>
       </c>
-      <c r="I40" s="1">
-        <v>0</v>
-      </c>
-      <c r="J40" s="1">
+      <c r="I40" s="2">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2">
         <v>-0.32479999999999998</v>
       </c>
-      <c r="K40" s="1">
+      <c r="K40" s="2">
         <v>-3.2000000000000002E-3</v>
       </c>
-      <c r="L40" s="1">
+      <c r="L40" s="2">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="M40" s="1">
+      <c r="M40" s="2">
         <v>4.5600000000000002E-2</v>
       </c>
-      <c r="N40" s="1">
+      <c r="N40" s="2">
         <v>-0.63100000000000001</v>
       </c>
-      <c r="O40" s="1">
+      <c r="O40" s="2">
         <v>-12.123200000000001</v>
       </c>
     </row>
@@ -2545,40 +2548,40 @@
       <c r="C41" s="1">
         <v>5.7541000000000002</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41" s="2">
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="E41" s="1">
-        <v>0</v>
-      </c>
-      <c r="F41" s="1">
+      <c r="E41" s="2">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2">
         <v>-0.15529999999999999</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G41" s="2">
         <v>1.77E-2</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H41" s="2">
         <v>1.84E-2</v>
       </c>
-      <c r="I41" s="1">
-        <v>0</v>
-      </c>
-      <c r="J41" s="1">
+      <c r="I41" s="2">
+        <v>0</v>
+      </c>
+      <c r="J41" s="2">
         <v>0.1608</v>
       </c>
-      <c r="K41" s="1">
+      <c r="K41" s="2">
         <v>-9.1999999999999998E-3</v>
       </c>
-      <c r="L41" s="1">
+      <c r="L41" s="2">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="M41" s="1">
+      <c r="M41" s="2">
         <v>-4.2200000000000001E-2</v>
       </c>
-      <c r="N41" s="1">
+      <c r="N41" s="2">
         <v>-7.1300000000000002E-2</v>
       </c>
-      <c r="O41" s="1">
+      <c r="O41" s="2">
         <v>-26.7789</v>
       </c>
     </row>

--- a/mainWidget/mainWidget/src/database/计算模型-跌落试验-45.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-跌落试验-45.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F3D244-9C49-489C-B0F7-D091AFBECD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E36328AF-1720-40FA-9F41-7298A3CEA633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{CB591892-9D69-40F9-A312-D4C0F059E1B0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="计算模型-跌落试验-45-1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>序号</t>
   </si>
@@ -65,126 +65,6 @@
   </si>
   <si>
     <t xml:space="preserve">M (mm) </t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>40</t>
   </si>
   <si>
     <t>8.8212 + 0.0022*B + 0.0000*C - 0.0262*D + 0.0009*E - 0.0029*F + 0.0000*G - 0.0848*H + 0.0015*I + 0.0007*J - 0.0096*K - 0.1352*L + 0.0134*M</t>
@@ -311,27 +191,349 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线 Light"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -339,24 +541,293 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="42">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -369,9 +840,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -379,44 +850,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -444,14 +915,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -479,9 +967,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -490,175 +995,151 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7F1A0C-4A91-4B8A-BD36-CA9C73539D24}">
   <dimension ref="A1:O41"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -705,1888 +1186,1888 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="C2">
         <v>8.8211999999999993</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>-2.6200000000000001E-2</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2">
         <v>-2.8999999999999998E-3</v>
       </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2">
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>-8.48E-2</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2">
         <v>1.5E-3</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2">
         <v>-9.5999999999999992E-3</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2">
         <v>-0.13519999999999999</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2">
         <v>1.34E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
-      <c r="A3" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>26.266200000000001</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3">
         <v>1E-3</v>
       </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>1.8800000000000001E-2</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3">
         <v>-3.3999999999999998E-3</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2">
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>5.7299999999999997E-2</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3">
         <v>-1.2999999999999999E-3</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3">
         <v>-1.4500000000000001E-2</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3">
         <v>-0.1913</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3">
         <v>-2.0589</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
-      <c r="A4" t="s">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>-25.203099999999999</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4">
         <v>7.1000000000000004E-3</v>
       </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>0.22270000000000001</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4">
         <v>-5.33E-2</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4">
         <v>4.6300000000000001E-2</v>
       </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2">
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>0.64959999999999996</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4">
         <v>3.9300000000000002E-2</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4">
         <v>5.4000000000000003E-3</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4">
         <v>0.17599999999999999</v>
       </c>
-      <c r="N4" s="2">
+      <c r="N4">
         <v>-1.6087</v>
       </c>
-      <c r="O4" s="2">
+      <c r="O4">
         <v>-13.3727</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
-      <c r="A5" t="s">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>-2075.7078999999999</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5">
         <v>3.8899999999999997E-2</v>
       </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>-0.27929999999999999</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5">
         <v>0.1024</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5">
         <v>0.19800000000000001</v>
       </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
         <v>-3.6566000000000001</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5">
         <v>-0.113</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5">
         <v>4.1099999999999998E-2</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5">
         <v>0.56310000000000004</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5">
         <v>4.2419000000000002</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5">
         <v>-40.209400000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
-      <c r="A6" t="s">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="C6">
         <v>-3930.1880999999998</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6">
         <v>0.12570000000000001</v>
       </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>0.88900000000000001</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6">
         <v>0.27</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6">
         <v>0.55059999999999998</v>
       </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>-9.8482000000000003</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6">
         <v>-0.13880000000000001</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6">
         <v>0.1172</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6">
         <v>1.0164</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6">
         <v>5.3682999999999996</v>
       </c>
-      <c r="O6" s="2">
+      <c r="O6">
         <v>-278.12110000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
-      <c r="A7" t="s">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="1">
+      <c r="C7">
         <v>24.685600000000001</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>-3.3999999999999998E-3</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7">
         <v>-2.3E-3</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>4.48E-2</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7">
         <v>1.8E-3</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7">
         <v>-1.7500000000000002E-2</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7">
         <v>-0.16439999999999999</v>
       </c>
-      <c r="O7" s="2">
+      <c r="O7">
         <v>-2.2593999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
-      <c r="A8" t="s">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="C8">
         <v>-0.46810000000000002</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8">
         <v>1E-4</v>
       </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8">
         <v>-2.0000000000000001E-4</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8">
         <v>1E-4</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8">
         <v>-2.9999999999999997E-4</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8">
         <v>-1.09E-2</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O8">
         <v>1.2800000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
-      <c r="A9" t="s">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="C9">
         <v>-4.5602999999999998</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>-6.1000000000000004E-3</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9">
         <v>-1.6000000000000001E-3</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9">
         <v>1.9E-3</v>
       </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
         <v>3.1399999999999997E-2</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9">
         <v>1.8E-3</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9">
         <v>1E-4</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9">
         <v>-4.9200000000000001E-2</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O9">
         <v>-0.1996</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
-      <c r="A10" t="s">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
         <v>23</v>
       </c>
-      <c r="B10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="1">
+      <c r="C10">
         <v>-20.006499999999999</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10">
         <v>-1.9E-3</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2">
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
         <v>-0.1207</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10">
         <v>-5.3E-3</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10">
         <v>1.38E-2</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10">
         <v>-0.1293</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10">
         <v>1.2594000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
-      <c r="A11" t="s">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
       </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="1">
+      <c r="C11">
         <v>-7.1607000000000003</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11">
         <v>2.35E-2</v>
       </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>-0.29310000000000003</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11">
         <v>-7.9799999999999996E-2</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11">
         <v>6.2899999999999998E-2</v>
       </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2">
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
         <v>-1.3003</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11">
         <v>-3.85E-2</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11">
         <v>1.6E-2</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11">
         <v>8.8400000000000006E-2</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11">
         <v>-1.7969999999999999</v>
       </c>
-      <c r="O11" s="2">
+      <c r="O11">
         <v>-9.6062999999999992</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
-      <c r="A12" t="s">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
         <v>25</v>
       </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="1">
+      <c r="C12">
         <v>32.298299999999998</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <v>-2.07E-2</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12">
         <v>-1.5E-3</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2">
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
         <v>-3.0999999999999999E-3</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12">
         <v>-6.9999999999999999E-4</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12">
         <v>-1.6299999999999999E-2</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12">
         <v>-0.16270000000000001</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12">
         <v>-1.8993</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
-      <c r="A13" t="s">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
         <v>26</v>
       </c>
-      <c r="B13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="1">
+      <c r="C13">
         <v>-0.1636</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13">
         <v>1E-4</v>
       </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
         <v>1.5E-3</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13">
         <v>-2.0000000000000001E-4</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2">
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13">
         <v>1E-4</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13">
         <v>-2.0000000000000001E-4</v>
       </c>
-      <c r="N13" s="2">
+      <c r="N13">
         <v>-1.3100000000000001E-2</v>
       </c>
-      <c r="O13" s="2">
+      <c r="O13">
         <v>-2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
-      <c r="A14" t="s">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
         <v>27</v>
       </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="1">
+      <c r="C14">
         <v>-4.6791999999999998</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14">
         <v>1E-4</v>
       </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>-1.1000000000000001E-3</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14">
         <v>-1.2999999999999999E-3</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14">
         <v>1.4E-3</v>
       </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2">
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
         <v>3.7900000000000003E-2</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14">
         <v>1E-4</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M14">
         <v>6.7999999999999996E-3</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N14">
         <v>-3.4099999999999998E-2</v>
       </c>
-      <c r="O14" s="2">
+      <c r="O14">
         <v>7.6200000000000004E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
-      <c r="A15" t="s">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
         <v>28</v>
       </c>
-      <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="1">
+      <c r="C15">
         <v>4.7222999999999997</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15">
         <v>-2.3E-3</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2">
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
         <v>-1.84E-2</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15">
         <v>-1.1999999999999999E-3</v>
       </c>
-      <c r="L15" s="2">
+      <c r="L15">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="M15" s="2">
+      <c r="M15">
         <v>1.2E-2</v>
       </c>
-      <c r="N15" s="2">
+      <c r="N15">
         <v>-0.18240000000000001</v>
       </c>
-      <c r="O15" s="2">
+      <c r="O15">
         <v>-0.49819999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
-      <c r="A16" t="s">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
         <v>29</v>
       </c>
-      <c r="B16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="1">
+      <c r="C16">
         <v>116.9363</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16">
         <v>1.7100000000000001E-2</v>
       </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
         <v>-7.6E-3</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16">
         <v>-4.2500000000000003E-2</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16">
         <v>5.2299999999999999E-2</v>
       </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2">
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
         <v>-0.999</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16">
         <v>-4.1000000000000002E-2</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="N16" s="2">
+      <c r="N16">
         <v>-1.6734</v>
       </c>
-      <c r="O16" s="2">
+      <c r="O16">
         <v>-17.1433</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
-      <c r="A17" t="s">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
         <v>30</v>
       </c>
-      <c r="B17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="1">
+      <c r="C17">
         <v>63.913400000000003</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
         <v>-4.24E-2</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17">
         <v>-1.7500000000000002E-2</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2">
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
         <v>-0.15140000000000001</v>
       </c>
-      <c r="K17" s="2">
+      <c r="K17">
         <v>1E-4</v>
       </c>
-      <c r="L17" s="2">
+      <c r="L17">
         <v>1.4E-3</v>
       </c>
-      <c r="M17" s="2">
+      <c r="M17">
         <v>-5.79E-2</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N17">
         <v>-8.6300000000000002E-2</v>
       </c>
-      <c r="O17" s="2">
+      <c r="O17">
         <v>-2.5954000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
-      <c r="A18" t="s">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
         <v>31</v>
       </c>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="1">
+      <c r="C18">
         <v>1.1828000000000001</v>
       </c>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
         <v>-5.0000000000000001E-4</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18">
         <v>-2.0000000000000001E-4</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2">
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="K18" s="2">
+      <c r="K18">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="L18" s="2">
+      <c r="L18">
         <v>1E-4</v>
       </c>
-      <c r="M18" s="2">
+      <c r="M18">
         <v>-1.4E-3</v>
       </c>
-      <c r="N18" s="2">
+      <c r="N18">
         <v>-1.0999999999999999E-2</v>
       </c>
-      <c r="O18" s="2">
+      <c r="O18">
         <v>3.7900000000000003E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
-      <c r="A19" t="s">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
         <v>32</v>
       </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="1">
+      <c r="C19">
         <v>-3.8458000000000001</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19">
         <v>1E-4</v>
       </c>
-      <c r="E19" s="2">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2">
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19">
         <v>-4.0000000000000002E-4</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2">
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
         <v>1.29E-2</v>
       </c>
-      <c r="K19" s="2">
+      <c r="K19">
         <v>1E-4</v>
       </c>
-      <c r="L19" s="2">
+      <c r="L19">
         <v>1E-4</v>
       </c>
-      <c r="M19" s="2">
+      <c r="M19">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="N19" s="2">
+      <c r="N19">
         <v>-1.38E-2</v>
       </c>
-      <c r="O19" s="2">
+      <c r="O19">
         <v>0.35310000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
-      <c r="A20" t="s">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
         <v>33</v>
       </c>
-      <c r="B20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="1">
+      <c r="C20">
         <v>4.0095999999999998</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
         <v>1.5E-3</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20">
         <v>-2.2000000000000001E-3</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2">
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
         <v>1.9E-2</v>
       </c>
-      <c r="K20" s="2">
+      <c r="K20">
         <v>-1E-4</v>
       </c>
-      <c r="L20" s="2">
+      <c r="L20">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="M20" s="2">
+      <c r="M20">
         <v>1.29E-2</v>
       </c>
-      <c r="N20" s="2">
+      <c r="N20">
         <v>-0.16250000000000001</v>
       </c>
-      <c r="O20" s="2">
+      <c r="O20">
         <v>-0.68130000000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
-      <c r="A21" t="s">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
         <v>34</v>
       </c>
-      <c r="B21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="1">
+      <c r="C21">
         <v>-116.33499999999999</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21">
         <v>2.35E-2</v>
       </c>
-      <c r="E21" s="2">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
         <v>-0.2989</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21">
         <v>-7.3800000000000004E-2</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21">
         <v>6.6600000000000006E-2</v>
       </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2">
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
         <v>-2.2766999999999999</v>
       </c>
-      <c r="K21" s="2">
+      <c r="K21">
         <v>-6.59E-2</v>
       </c>
-      <c r="L21" s="2">
+      <c r="L21">
         <v>1.66E-2</v>
       </c>
-      <c r="M21" s="2">
+      <c r="M21">
         <v>8.1900000000000001E-2</v>
       </c>
-      <c r="N21" s="2">
+      <c r="N21">
         <v>-1.0645</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O21">
         <v>-11.442299999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
-      <c r="A22" t="s">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
         <v>35</v>
       </c>
-      <c r="B22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="1">
+      <c r="C22">
         <v>65.199799999999996</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="E22" s="2">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2">
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
         <v>-6.7199999999999996E-2</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22">
         <v>-1.95E-2</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22">
         <v>6.7999999999999996E-3</v>
       </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
         <v>2.35E-2</v>
       </c>
-      <c r="K22" s="2">
+      <c r="K22">
         <v>-4.7000000000000002E-3</v>
       </c>
-      <c r="L22" s="2">
+      <c r="L22">
         <v>1.4E-3</v>
       </c>
-      <c r="M22" s="2">
+      <c r="M22">
         <v>-5.2999999999999999E-2</v>
       </c>
-      <c r="N22" s="2">
+      <c r="N22">
         <v>-0.1115</v>
       </c>
-      <c r="O22" s="2">
+      <c r="O22">
         <v>-1.7663</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
-      <c r="A23" t="s">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
         <v>36</v>
       </c>
-      <c r="B23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="1">
+      <c r="C23">
         <v>0.22389999999999999</v>
       </c>
-      <c r="D23" s="2">
-        <v>0</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2">
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="G23" s="2">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2">
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2">
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
         <v>1.4200000000000001E-2</v>
       </c>
-      <c r="K23" s="2">
+      <c r="K23">
         <v>1E-4</v>
       </c>
-      <c r="L23" s="2">
+      <c r="L23">
         <v>1E-4</v>
       </c>
-      <c r="M23" s="2">
+      <c r="M23">
         <v>-5.0000000000000001E-4</v>
       </c>
-      <c r="N23" s="2">
+      <c r="N23">
         <v>-1.2800000000000001E-2</v>
       </c>
-      <c r="O23" s="2">
+      <c r="O23">
         <v>1.6899999999999998E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
-      <c r="A24" t="s">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
         <v>37</v>
       </c>
-      <c r="B24" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="1">
+      <c r="C24">
         <v>-2.1697000000000002</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24">
         <v>1E-4</v>
       </c>
-      <c r="E24" s="2">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2">
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
         <v>-3.5999999999999999E-3</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24">
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="I24" s="2">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2">
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
         <v>6.7999999999999996E-3</v>
       </c>
-      <c r="K24" s="2">
+      <c r="K24">
         <v>1E-4</v>
       </c>
-      <c r="L24" s="2">
+      <c r="L24">
         <v>1E-4</v>
       </c>
-      <c r="M24" s="2">
+      <c r="M24">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="N24" s="2">
+      <c r="N24">
         <v>-3.15E-2</v>
       </c>
-      <c r="O24" s="2">
+      <c r="O24">
         <v>-2.5499999999999998E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
-      <c r="A25" t="s">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
         <v>38</v>
       </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="1">
+      <c r="C25">
         <v>-1.7814000000000001</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="E25" s="2">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2">
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25">
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25">
         <v>1.4E-3</v>
       </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2">
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="K25" s="2">
+      <c r="K25">
         <v>-4.0000000000000002E-4</v>
       </c>
-      <c r="L25" s="2">
+      <c r="L25">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="M25" s="2">
+      <c r="M25">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="N25" s="2">
+      <c r="N25">
         <v>-5.5599999999999997E-2</v>
       </c>
-      <c r="O25" s="2">
+      <c r="O25">
         <v>5.8099999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
-      <c r="A26" t="s">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
         <v>39</v>
       </c>
-      <c r="B26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" s="1">
+      <c r="C26">
         <v>-90.206299999999999</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26">
         <v>1.6799999999999999E-2</v>
       </c>
-      <c r="E26" s="2">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2">
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
         <v>-0.18149999999999999</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26">
         <v>-6.2E-2</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26">
         <v>4.41E-2</v>
       </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2">
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
         <v>-1.5721000000000001</v>
       </c>
-      <c r="K26" s="2">
+      <c r="K26">
         <v>-5.28E-2</v>
       </c>
-      <c r="L26" s="2">
+      <c r="L26">
         <v>1.26E-2</v>
       </c>
-      <c r="M26" s="2">
+      <c r="M26">
         <v>7.17E-2</v>
       </c>
-      <c r="N26" s="2">
+      <c r="N26">
         <v>-0.79459999999999997</v>
       </c>
-      <c r="O26" s="2">
+      <c r="O26">
         <v>-5.8758999999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
-      <c r="A27" t="s">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
         <v>40</v>
       </c>
-      <c r="B27" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" s="1">
+      <c r="C27">
         <v>23.620799999999999</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="E27" s="2">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2">
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G27">
         <v>1E-4</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="I27" s="2">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2">
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
         <v>0.13389999999999999</v>
       </c>
-      <c r="K27" s="2">
+      <c r="K27">
         <v>-3.5000000000000001E-3</v>
       </c>
-      <c r="L27" s="2">
+      <c r="L27">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="M27" s="2">
+      <c r="M27">
         <v>-1.04E-2</v>
       </c>
-      <c r="N27" s="2">
+      <c r="N27">
         <v>-0.183</v>
       </c>
-      <c r="O27" s="2">
+      <c r="O27">
         <v>-1.6662999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
-      <c r="A28" t="s">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
         <v>41</v>
       </c>
-      <c r="B28" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" s="1">
+      <c r="C28">
         <v>-0.42949999999999999</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28">
         <v>1E-4</v>
       </c>
-      <c r="E28" s="2">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2">
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
         <v>-1.1000000000000001E-3</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G28">
         <v>-1E-4</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
-      <c r="J28" s="2">
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="K28" s="2">
-        <v>0</v>
-      </c>
-      <c r="L28" s="2">
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
         <v>1E-4</v>
       </c>
-      <c r="M28" s="2">
+      <c r="M28">
         <v>1E-3</v>
       </c>
-      <c r="N28" s="2">
+      <c r="N28">
         <v>-1.6E-2</v>
       </c>
-      <c r="O28" s="2">
+      <c r="O28">
         <v>6.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
-      <c r="A29" t="s">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
         <v>42</v>
       </c>
-      <c r="B29" t="s">
-        <v>82</v>
-      </c>
-      <c r="C29" s="1">
+      <c r="C29">
         <v>-1.9615</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="E29" s="2">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2">
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
         <v>-7.1999999999999998E-3</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29">
         <v>-1.1999999999999999E-3</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29">
         <v>1.5E-3</v>
       </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2">
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
         <v>2.92E-2</v>
       </c>
-      <c r="K29" s="2">
+      <c r="K29">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="L29" s="2">
+      <c r="L29">
         <v>1E-4</v>
       </c>
-      <c r="M29" s="2">
+      <c r="M29">
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="N29" s="2">
+      <c r="N29">
         <v>-5.3900000000000003E-2</v>
       </c>
-      <c r="O29" s="2">
+      <c r="O29">
         <v>-0.29549999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
-      <c r="A30" t="s">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
         <v>43</v>
       </c>
-      <c r="B30" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" s="1">
+      <c r="C30">
         <v>-1.837</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="E30" s="2">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2">
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
         <v>-4.7000000000000002E-3</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G30">
         <v>-8.9999999999999998E-4</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2">
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
         <v>5.7500000000000002E-2</v>
       </c>
-      <c r="K30" s="2">
+      <c r="K30">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="L30" s="2">
+      <c r="L30">
         <v>1E-4</v>
       </c>
-      <c r="M30" s="2">
+      <c r="M30">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="N30" s="2">
+      <c r="N30">
         <v>-5.3499999999999999E-2</v>
       </c>
-      <c r="O30" s="2">
+      <c r="O30">
         <v>7.7999999999999996E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
-      <c r="A31" t="s">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
         <v>44</v>
       </c>
-      <c r="B31" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" s="1">
+      <c r="C31">
         <v>84.4529</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31">
         <v>1.11E-2</v>
       </c>
-      <c r="E31" s="2">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2">
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
         <v>8.1900000000000001E-2</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G31">
         <v>-1.3299999999999999E-2</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31">
         <v>2.58E-2</v>
       </c>
-      <c r="I31" s="2">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2">
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
         <v>-0.1037</v>
       </c>
-      <c r="K31" s="2">
+      <c r="K31">
         <v>-2.5899999999999999E-2</v>
       </c>
-      <c r="L31" s="2">
+      <c r="L31">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="M31" s="2">
+      <c r="M31">
         <v>5.9200000000000003E-2</v>
       </c>
-      <c r="N31" s="2">
+      <c r="N31">
         <v>-1.2926</v>
       </c>
-      <c r="O31" s="2">
+      <c r="O31">
         <v>-6.0380000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
-      <c r="A32" t="s">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
         <v>45</v>
       </c>
-      <c r="B32" t="s">
-        <v>85</v>
-      </c>
-      <c r="C32" s="1">
+      <c r="C32">
         <v>19.222999999999999</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="E32" s="2">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2">
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G32">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32">
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="I32" s="2">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2">
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="K32" s="2">
+      <c r="K32">
         <v>-2.5000000000000001E-3</v>
       </c>
-      <c r="L32" s="2">
+      <c r="L32">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="M32" s="2">
+      <c r="M32">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="N32" s="2">
+      <c r="N32">
         <v>-0.22289999999999999</v>
       </c>
-      <c r="O32" s="2">
+      <c r="O32">
         <v>-1.8352999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
-      <c r="A33" t="s">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
         <v>46</v>
       </c>
-      <c r="B33" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" s="1">
+      <c r="C33">
         <v>-0.45939999999999998</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33">
         <v>1E-4</v>
       </c>
-      <c r="E33" s="2">
-        <v>0</v>
-      </c>
-      <c r="F33" s="2">
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G33">
         <v>1E-4</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="I33" s="2">
-        <v>0</v>
-      </c>
-      <c r="J33" s="2">
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="K33" s="2">
-        <v>0</v>
-      </c>
-      <c r="L33" s="2">
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
         <v>1E-4</v>
       </c>
-      <c r="M33" s="2">
+      <c r="M33">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N33" s="2">
+      <c r="N33">
         <v>-1.5299999999999999E-2</v>
       </c>
-      <c r="O33" s="2">
+      <c r="O33">
         <v>-2.3699999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
-      <c r="A34" t="s">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
         <v>47</v>
       </c>
-      <c r="B34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="1">
+      <c r="C34">
         <v>-2.1200999999999999</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34">
         <v>1E-4</v>
       </c>
-      <c r="E34" s="2">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2">
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
         <v>-1.24E-2</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G34">
         <v>-1.6999999999999999E-3</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="I34" s="2">
-        <v>0</v>
-      </c>
-      <c r="J34" s="2">
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="K34" s="2">
+      <c r="K34">
         <v>1.5E-3</v>
       </c>
-      <c r="L34" s="2">
+      <c r="L34">
         <v>1E-4</v>
       </c>
-      <c r="M34" s="2">
+      <c r="M34">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="N34" s="2">
+      <c r="N34">
         <v>-7.4999999999999997E-2</v>
       </c>
-      <c r="O34" s="2">
+      <c r="O34">
         <v>-0.52610000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
-      <c r="A35" t="s">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
         <v>48</v>
       </c>
-      <c r="B35" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" s="1">
+      <c r="C35">
         <v>-1.4162999999999999</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="E35" s="2">
-        <v>0</v>
-      </c>
-      <c r="F35" s="2">
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
         <v>-1.5E-3</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G35">
         <v>-8.0000000000000004E-4</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="I35" s="2">
-        <v>0</v>
-      </c>
-      <c r="J35" s="2">
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
         <v>2.9700000000000001E-2</v>
       </c>
-      <c r="K35" s="2">
+      <c r="K35">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="L35" s="2">
+      <c r="L35">
         <v>1E-4</v>
       </c>
-      <c r="M35" s="2">
+      <c r="M35">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="N35" s="2">
+      <c r="N35">
         <v>-3.8300000000000001E-2</v>
       </c>
-      <c r="O35" s="2">
+      <c r="O35">
         <v>-7.7399999999999997E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
-      <c r="A36" t="s">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
         <v>49</v>
       </c>
-      <c r="B36" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" s="1">
+      <c r="C36">
         <v>54.6312</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36">
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="E36" s="2">
-        <v>0</v>
-      </c>
-      <c r="F36" s="2">
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G36">
         <v>-2.06E-2</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36">
         <v>1.72E-2</v>
       </c>
-      <c r="I36" s="2">
-        <v>0</v>
-      </c>
-      <c r="J36" s="2">
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
         <v>-3.8999999999999998E-3</v>
       </c>
-      <c r="K36" s="2">
+      <c r="K36">
         <v>-1.21E-2</v>
       </c>
-      <c r="L36" s="2">
+      <c r="L36">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="M36" s="2">
+      <c r="M36">
         <v>5.8400000000000001E-2</v>
       </c>
-      <c r="N36" s="2">
+      <c r="N36">
         <v>-1.1404000000000001</v>
       </c>
-      <c r="O36" s="2">
+      <c r="O36">
         <v>-3.5251999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
-      <c r="A37" t="s">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
         <v>50</v>
       </c>
-      <c r="B37" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" s="1">
+      <c r="C37">
         <v>-9.3774999999999995</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="E37" s="2">
-        <v>0</v>
-      </c>
-      <c r="F37" s="2">
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
         <v>-1.4E-2</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G37">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="I37" s="2">
-        <v>0</v>
-      </c>
-      <c r="J37" s="2">
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
         <v>-0.14399999999999999</v>
       </c>
-      <c r="K37" s="2">
+      <c r="K37">
         <v>-1.1000000000000001E-3</v>
       </c>
-      <c r="L37" s="2">
+      <c r="L37">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="M37" s="2">
+      <c r="M37">
         <v>-3.3E-3</v>
       </c>
-      <c r="N37" s="2">
+      <c r="N37">
         <v>-0.15570000000000001</v>
       </c>
-      <c r="O37" s="2">
+      <c r="O37">
         <v>0.13869999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
-      <c r="A38" t="s">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
         <v>51</v>
       </c>
-      <c r="B38" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" s="1">
+      <c r="C38">
         <v>8.0661000000000005</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38">
         <v>2.8E-3</v>
       </c>
-      <c r="E38" s="2">
-        <v>0</v>
-      </c>
-      <c r="F38" s="2">
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
         <v>1.43E-2</v>
       </c>
-      <c r="G38" s="2">
+      <c r="G38">
         <v>-8.0000000000000004E-4</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="I38" s="2">
-        <v>0</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
         <v>3.8600000000000002E-2</v>
       </c>
-      <c r="K38" s="2">
+      <c r="K38">
         <v>-8.9999999999999998E-4</v>
       </c>
-      <c r="L38" s="2">
+      <c r="L38">
         <v>1E-3</v>
       </c>
-      <c r="M38" s="2">
+      <c r="M38">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="N38" s="2">
+      <c r="N38">
         <v>-0.25369999999999998</v>
       </c>
-      <c r="O38" s="2">
+      <c r="O38">
         <v>-1.8654999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
-      <c r="A39" t="s">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
         <v>52</v>
       </c>
-      <c r="B39" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" s="1">
+      <c r="C39">
         <v>-52.941099999999999</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39">
         <v>1.01E-2</v>
       </c>
-      <c r="E39" s="2">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2">
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
         <v>0.14050000000000001</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G39">
         <v>-2.6100000000000002E-2</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39">
         <v>4.9500000000000002E-2</v>
       </c>
-      <c r="I39" s="2">
-        <v>0</v>
-      </c>
-      <c r="J39" s="2">
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
         <v>0.6855</v>
       </c>
-      <c r="K39" s="2">
+      <c r="K39">
         <v>3.1300000000000001E-2</v>
       </c>
-      <c r="L39" s="2">
+      <c r="L39">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="M39" s="2">
+      <c r="M39">
         <v>0.46079999999999999</v>
       </c>
-      <c r="N39" s="2">
+      <c r="N39">
         <v>-2.7578</v>
       </c>
-      <c r="O39" s="2">
+      <c r="O39">
         <v>-19.533200000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
-      <c r="A40" t="s">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
         <v>53</v>
       </c>
-      <c r="B40" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" s="1">
+      <c r="C40">
         <v>29.927399999999999</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40">
         <v>1.24E-2</v>
       </c>
-      <c r="E40" s="2">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2">
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
         <v>0.12089999999999999</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G40">
         <v>-2.47E-2</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40">
         <v>1.2800000000000001E-2</v>
       </c>
-      <c r="I40" s="2">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2">
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
         <v>-0.32479999999999998</v>
       </c>
-      <c r="K40" s="2">
+      <c r="K40">
         <v>-3.2000000000000002E-3</v>
       </c>
-      <c r="L40" s="2">
+      <c r="L40">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="M40" s="2">
+      <c r="M40">
         <v>4.5600000000000002E-2</v>
       </c>
-      <c r="N40" s="2">
+      <c r="N40">
         <v>-0.63100000000000001</v>
       </c>
-      <c r="O40" s="2">
+      <c r="O40">
         <v>-12.123200000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
-      <c r="A41" t="s">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
         <v>54</v>
       </c>
-      <c r="B41" t="s">
-        <v>94</v>
-      </c>
-      <c r="C41" s="1">
+      <c r="C41">
         <v>5.7541000000000002</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41">
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="E41" s="2">
-        <v>0</v>
-      </c>
-      <c r="F41" s="2">
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
         <v>-0.15529999999999999</v>
       </c>
-      <c r="G41" s="2">
+      <c r="G41">
         <v>1.77E-2</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41">
         <v>1.84E-2</v>
       </c>
-      <c r="I41" s="2">
-        <v>0</v>
-      </c>
-      <c r="J41" s="2">
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
         <v>0.1608</v>
       </c>
-      <c r="K41" s="2">
+      <c r="K41">
         <v>-9.1999999999999998E-3</v>
       </c>
-      <c r="L41" s="2">
+      <c r="L41">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="M41" s="2">
+      <c r="M41">
         <v>-4.2200000000000001E-2</v>
       </c>
-      <c r="N41" s="2">
+      <c r="N41">
         <v>-7.1300000000000002E-2</v>
       </c>
-      <c r="O41" s="2">
+      <c r="O41">
         <v>-26.7789</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/mainWidget/mainWidget/src/database/计算模型-跌落试验-45.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-跌落试验-45.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E36328AF-1720-40FA-9F41-7298A3CEA633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2F0211-ACEE-4B16-B83F-08D900CADB8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{CB591892-9D69-40F9-A312-D4C0F059E1B0}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="779">
   <si>
     <t>序号</t>
   </si>
@@ -185,19 +185,2198 @@
   </si>
   <si>
     <t>5.7541 + 0.0127*B + 0.0000*C - 0.1553*D + 0.0177*E + 0.0184*F + 0.0000*G + 0.1608*H - 0.0092*I + 0.0051*J - 0.0422*K - 0.0713*L - 26.7789*M</t>
+  </si>
+  <si>
+    <t>98.0979 +0.0062*B + 0.0*C +0.0831*D +0.0543*E +0.0154*F + 0.0*G -0.7403*H +0.0248*I +0.0168*J +0.0*K +0.3543*L -25.7968*M</t>
+  </si>
+  <si>
+    <t>98.0979</t>
+  </si>
+  <si>
+    <t>0.0062</t>
+  </si>
+  <si>
+    <t>0.0000</t>
+  </si>
+  <si>
+    <t>0.0831</t>
+  </si>
+  <si>
+    <t>0.0543</t>
+  </si>
+  <si>
+    <t>0.0154</t>
+  </si>
+  <si>
+    <t>-0.7403</t>
+  </si>
+  <si>
+    <t>0.0248</t>
+  </si>
+  <si>
+    <t>0.0168</t>
+  </si>
+  <si>
+    <t>0.3543</t>
+  </si>
+  <si>
+    <t>-25.7968</t>
+  </si>
+  <si>
+    <t>-371.9205 +0.0118*B + 0.0*C -0.2315*D -0.0646*E +0.0*F + 0.0*G -1.6695*H -0.0039*I +0.0001*J +0.0*K +1.2058*L -18.4662*M</t>
+  </si>
+  <si>
+    <t>-371.9205</t>
+  </si>
+  <si>
+    <t>0.0118</t>
+  </si>
+  <si>
+    <t>-0.2315</t>
+  </si>
+  <si>
+    <t>-0.0646</t>
+  </si>
+  <si>
+    <t>-1.6695</t>
+  </si>
+  <si>
+    <t>-0.0039</t>
+  </si>
+  <si>
+    <t>0.0001</t>
+  </si>
+  <si>
+    <t>1.2058</t>
+  </si>
+  <si>
+    <t>-18.4662</t>
+  </si>
+  <si>
+    <t>-111.4991 +0.0*B + 0.0*C -0.0634*D +0.0026*E +0.0*F + 0.0*G -0.0125*H -0.0247*I +0.0024*J +0.0*K +1.5624*L -11.9179*M</t>
+  </si>
+  <si>
+    <t>-111.4991</t>
+  </si>
+  <si>
+    <t>-0.0634</t>
+  </si>
+  <si>
+    <t>0.0026</t>
+  </si>
+  <si>
+    <t>-0.0125</t>
+  </si>
+  <si>
+    <t>-0.0247</t>
+  </si>
+  <si>
+    <t>0.0024</t>
+  </si>
+  <si>
+    <t>1.5624</t>
+  </si>
+  <si>
+    <t>-11.9179</t>
+  </si>
+  <si>
+    <t>-661.02 +0.0203*B + 0.0*C -0.1465*D +0.0062*E +0.0*F + 0.0*G -2.0458*H -0.0066*I +0.0164*J +0.0871*K -0.2528*L -20.7899*M</t>
+  </si>
+  <si>
+    <t>-661.0200</t>
+  </si>
+  <si>
+    <t>0.0203</t>
+  </si>
+  <si>
+    <t>-0.1465</t>
+  </si>
+  <si>
+    <t>-2.0458</t>
+  </si>
+  <si>
+    <t>-0.0066</t>
+  </si>
+  <si>
+    <t>0.0164</t>
+  </si>
+  <si>
+    <t>0.0871</t>
+  </si>
+  <si>
+    <t>-0.2528</t>
+  </si>
+  <si>
+    <t>-20.7899</t>
+  </si>
+  <si>
+    <t>-866.5269 +0.0*B + 0.0*C -0.0531*D +0.0372*E +0.0523*F + 0.0*G -2.5648*H -0.0037*I +0.0011*J +0.0*K +0.4181*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>-866.5269</t>
+  </si>
+  <si>
+    <t>-0.0531</t>
+  </si>
+  <si>
+    <t>0.0372</t>
+  </si>
+  <si>
+    <t>0.0523</t>
+  </si>
+  <si>
+    <t>-2.5648</t>
+  </si>
+  <si>
+    <t>-0.0037</t>
+  </si>
+  <si>
+    <t>0.0011</t>
+  </si>
+  <si>
+    <t>0.4181</t>
+  </si>
+  <si>
+    <t>1.5113</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0*B + 0.0*C -0.0345*D +0.0106*E +0.0927*F + 0.0*G -1.0327*H -0.0152*I +0.0001*J +0.0*K +0.6033*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>140.3236</t>
+  </si>
+  <si>
+    <t>-0.0345</t>
+  </si>
+  <si>
+    <t>0.0106</t>
+  </si>
+  <si>
+    <t>0.0927</t>
+  </si>
+  <si>
+    <t>-1.0327</t>
+  </si>
+  <si>
+    <t>-0.0152</t>
+  </si>
+  <si>
+    <t>0.6033</t>
+  </si>
+  <si>
+    <t>-179.6439 +0.0229*B + 0.0*C +0.0479*D -0.0251*E +0.0534*F + 0.0*G +0.8226*H -0.0118*I +0.0277*J +0.0*K +0.612*L -8.8164*M</t>
+  </si>
+  <si>
+    <t>-179.6439</t>
+  </si>
+  <si>
+    <t>0.0229</t>
+  </si>
+  <si>
+    <t>0.0479</t>
+  </si>
+  <si>
+    <t>-0.0251</t>
+  </si>
+  <si>
+    <t>0.0534</t>
+  </si>
+  <si>
+    <t>0.8226</t>
+  </si>
+  <si>
+    <t>-0.0118</t>
+  </si>
+  <si>
+    <t>0.0277</t>
+  </si>
+  <si>
+    <t>0.6120</t>
+  </si>
+  <si>
+    <t>-8.8164</t>
+  </si>
+  <si>
+    <t>-290.5001 +0.0096*B + 0.0*C -0.2406*D -0.0095*E +0.0531*F + 0.0*G +0.8226*H -0.0228*I +0.0001*J +0.0*K +0.6982*L -1.3604*M</t>
+  </si>
+  <si>
+    <t>-290.5001</t>
+  </si>
+  <si>
+    <t>0.0096</t>
+  </si>
+  <si>
+    <t>-0.2406</t>
+  </si>
+  <si>
+    <t>-0.0095</t>
+  </si>
+  <si>
+    <t>0.0531</t>
+  </si>
+  <si>
+    <t>-0.0228</t>
+  </si>
+  <si>
+    <t>0.6982</t>
+  </si>
+  <si>
+    <t>-1.3604</t>
+  </si>
+  <si>
+    <t>-403.1904 +0.0158*B + 0.0*C +0.0154*D +0.034*E +0.0*F + 0.0*G -0.8519*H -0.0199*I +0.0001*J +0.1041*K +0.0946*L -11.3438*M</t>
+  </si>
+  <si>
+    <t>-403.1904</t>
+  </si>
+  <si>
+    <t>0.0158</t>
+  </si>
+  <si>
+    <t>0.0340</t>
+  </si>
+  <si>
+    <t>-0.8519</t>
+  </si>
+  <si>
+    <t>-0.0199</t>
+  </si>
+  <si>
+    <t>0.1041</t>
+  </si>
+  <si>
+    <t>0.0946</t>
+  </si>
+  <si>
+    <t>-11.3438</t>
+  </si>
+  <si>
+    <t>-259.0399 +0.0*B + 0.0*C -0.0482*D -0.014*E +0.0*F + 0.0*G -0.6533*H -0.0019*I +0.0321*J +0.0876*K +0.0914*L -13.798*M</t>
+  </si>
+  <si>
+    <t>-259.0399</t>
+  </si>
+  <si>
+    <t>-0.0482</t>
+  </si>
+  <si>
+    <t>-0.0140</t>
+  </si>
+  <si>
+    <t>-0.6533</t>
+  </si>
+  <si>
+    <t>-0.0019</t>
+  </si>
+  <si>
+    <t>0.0321</t>
+  </si>
+  <si>
+    <t>0.0876</t>
+  </si>
+  <si>
+    <t>0.0914</t>
+  </si>
+  <si>
+    <t>-13.7980</t>
+  </si>
+  <si>
+    <t>-1081.5267 +0.0079*B + 0.0*C +0.0109*D +0.0887*E +0.018*F + 0.0*G -0.101*H -0.0118*I +0.0001*J +0.2192*K +0.5474*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>-1081.5267</t>
+  </si>
+  <si>
+    <t>0.0079</t>
+  </si>
+  <si>
+    <t>0.0109</t>
+  </si>
+  <si>
+    <t>0.0887</t>
+  </si>
+  <si>
+    <t>0.0180</t>
+  </si>
+  <si>
+    <t>-0.1010</t>
+  </si>
+  <si>
+    <t>0.2192</t>
+  </si>
+  <si>
+    <t>0.5474</t>
+  </si>
+  <si>
+    <t>-588.5848 +0.0288*B + 0.0*C -0.1687*D +0.02*E +0.1703*F + 0.0*G -1.6429*H -0.0239*I +0.0077*J +0.0*K -1.5765*L -9.3866*M</t>
+  </si>
+  <si>
+    <t>-588.5848</t>
+  </si>
+  <si>
+    <t>0.0288</t>
+  </si>
+  <si>
+    <t>-0.1687</t>
+  </si>
+  <si>
+    <t>0.0200</t>
+  </si>
+  <si>
+    <t>0.1703</t>
+  </si>
+  <si>
+    <t>-1.6429</t>
+  </si>
+  <si>
+    <t>-0.0239</t>
+  </si>
+  <si>
+    <t>0.0077</t>
+  </si>
+  <si>
+    <t>-1.5765</t>
+  </si>
+  <si>
+    <t>-9.3866</t>
+  </si>
+  <si>
+    <t>-663.2629 +0.0152*B + 0.0*C -0.1094*D +0.0552*E +0.0*F + 0.0*G -0.8452*H +0.0074*I +0.0001*J +0.0948*K +1.0596*L -61.0884*M</t>
+  </si>
+  <si>
+    <t>-663.2629</t>
+  </si>
+  <si>
+    <t>0.0152</t>
+  </si>
+  <si>
+    <t>-0.1094</t>
+  </si>
+  <si>
+    <t>0.0552</t>
+  </si>
+  <si>
+    <t>-0.8452</t>
+  </si>
+  <si>
+    <t>0.0074</t>
+  </si>
+  <si>
+    <t>0.0948</t>
+  </si>
+  <si>
+    <t>1.0596</t>
+  </si>
+  <si>
+    <t>-61.0884</t>
+  </si>
+  <si>
+    <t>-54.3094 +0.0121*B + 0.0*C +0.0995*D -0.0467*E +0.0*F + 0.0*G +0.162*H -0.0043*I +0.0098*J +0.111*K -0.7734*L -4.3371*M</t>
+  </si>
+  <si>
+    <t>-54.3094</t>
+  </si>
+  <si>
+    <t>0.0121</t>
+  </si>
+  <si>
+    <t>0.0995</t>
+  </si>
+  <si>
+    <t>-0.0467</t>
+  </si>
+  <si>
+    <t>0.1620</t>
+  </si>
+  <si>
+    <t>-0.0043</t>
+  </si>
+  <si>
+    <t>0.0098</t>
+  </si>
+  <si>
+    <t>0.1110</t>
+  </si>
+  <si>
+    <t>-0.7734</t>
+  </si>
+  <si>
+    <t>-4.3371</t>
+  </si>
+  <si>
+    <t>-1.3524 +0.0*B + 0.0*C +0.2327*D +0.0159*E +0.0*F + 0.0*G +0.3226*H -0.0331*I +0.0171*J +0.2214*K -0.9031*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>-1.3524</t>
+  </si>
+  <si>
+    <t>0.2327</t>
+  </si>
+  <si>
+    <t>0.0159</t>
+  </si>
+  <si>
+    <t>0.3226</t>
+  </si>
+  <si>
+    <t>-0.0331</t>
+  </si>
+  <si>
+    <t>0.0171</t>
+  </si>
+  <si>
+    <t>0.2214</t>
+  </si>
+  <si>
+    <t>-0.9031</t>
+  </si>
+  <si>
+    <t>57.1083 +0.0203*B + 0.0*C +0.2365*D -0.0105*E +0.0*F + 0.0*G -1.5223*H -0.0295*I +0.0053*J +0.1102*K +0.1091*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>57.1083</t>
+  </si>
+  <si>
+    <t>0.2365</t>
+  </si>
+  <si>
+    <t>-0.0105</t>
+  </si>
+  <si>
+    <t>-1.5223</t>
+  </si>
+  <si>
+    <t>-0.0295</t>
+  </si>
+  <si>
+    <t>0.0053</t>
+  </si>
+  <si>
+    <t>0.1102</t>
+  </si>
+  <si>
+    <t>0.1091</t>
+  </si>
+  <si>
+    <t>-138.1275 +0.0295*B + 0.0*C -0.029*D +0.0981*E +0.0703*F + 0.0*G -1.4837*H -0.0353*I +0.013*J +0.0335*K +0.5124*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>-138.1275</t>
+  </si>
+  <si>
+    <t>0.0295</t>
+  </si>
+  <si>
+    <t>-0.0290</t>
+  </si>
+  <si>
+    <t>0.0981</t>
+  </si>
+  <si>
+    <t>0.0703</t>
+  </si>
+  <si>
+    <t>-1.4837</t>
+  </si>
+  <si>
+    <t>-0.0353</t>
+  </si>
+  <si>
+    <t>0.0130</t>
+  </si>
+  <si>
+    <t>0.0335</t>
+  </si>
+  <si>
+    <t>0.5124</t>
+  </si>
+  <si>
+    <t>-180.0438 +0.0*B + 0.0*C -0.1826*D -0.0178*E +0.0851*F + 0.0*G -0.2054*H -0.0393*I +0.0087*J +0.1162*K -0.9614*L -6.7595*M</t>
+  </si>
+  <si>
+    <t>-180.0438</t>
+  </si>
+  <si>
+    <t>-0.1826</t>
+  </si>
+  <si>
+    <t>-0.0178</t>
+  </si>
+  <si>
+    <t>0.0851</t>
+  </si>
+  <si>
+    <t>-0.2054</t>
+  </si>
+  <si>
+    <t>-0.0393</t>
+  </si>
+  <si>
+    <t>0.0087</t>
+  </si>
+  <si>
+    <t>0.1162</t>
+  </si>
+  <si>
+    <t>-0.9614</t>
+  </si>
+  <si>
+    <t>-6.7595</t>
+  </si>
+  <si>
+    <t>-116.0503 +0.0*B + 0.0*C +0.0475*D +0.019*E +0.0995*F + 0.0*G +0.7967*H -0.0423*I +0.0001*J +0.1339*K +0.3278*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>-116.0503</t>
+  </si>
+  <si>
+    <t>0.0475</t>
+  </si>
+  <si>
+    <t>0.0190</t>
+  </si>
+  <si>
+    <t>0.7967</t>
+  </si>
+  <si>
+    <t>-0.0423</t>
+  </si>
+  <si>
+    <t>0.1339</t>
+  </si>
+  <si>
+    <t>0.3278</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0166*B + 0.0*C +0.143*D +0.0334*E +0.072*F + 0.0*G -0.8371*H +0.0062*I +0.0001*J +0.0317*K -0.5938*L -8.976*M</t>
+  </si>
+  <si>
+    <t>0.0166</t>
+  </si>
+  <si>
+    <t>0.1430</t>
+  </si>
+  <si>
+    <t>0.0334</t>
+  </si>
+  <si>
+    <t>0.0720</t>
+  </si>
+  <si>
+    <t>-0.8371</t>
+  </si>
+  <si>
+    <t>0.0317</t>
+  </si>
+  <si>
+    <t>-0.5938</t>
+  </si>
+  <si>
+    <t>-8.9760</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0*B + 0.0*C +0.0878*D -0.0605*E +0.0002*F + 0.0*G +0.8226*H -0.0096*I +0.0001*J +0.0*K +0.4807*L -34.0315*M</t>
+  </si>
+  <si>
+    <t>0.0878</t>
+  </si>
+  <si>
+    <t>-0.0605</t>
+  </si>
+  <si>
+    <t>0.0002</t>
+  </si>
+  <si>
+    <t>-0.0096</t>
+  </si>
+  <si>
+    <t>0.4807</t>
+  </si>
+  <si>
+    <t>-34.0315</t>
+  </si>
+  <si>
+    <t>-38.7675 +0.0089*B + 0.0*C -0.0765*D +0.077*E +0.0708*F + 0.0*G -2.8775*H -0.0068*I +0.0001*J +0.1797*K -0.8772*L -15.0409*M</t>
+  </si>
+  <si>
+    <t>-38.7675</t>
+  </si>
+  <si>
+    <t>0.0089</t>
+  </si>
+  <si>
+    <t>-0.0765</t>
+  </si>
+  <si>
+    <t>0.0770</t>
+  </si>
+  <si>
+    <t>0.0708</t>
+  </si>
+  <si>
+    <t>-2.8775</t>
+  </si>
+  <si>
+    <t>-0.0068</t>
+  </si>
+  <si>
+    <t>0.1797</t>
+  </si>
+  <si>
+    <t>-0.8772</t>
+  </si>
+  <si>
+    <t>-15.0409</t>
+  </si>
+  <si>
+    <t>102.1381 +0.0209*B + 0.0*C -0.1439*D -0.0137*E +0.0*F + 0.0*G -1.2405*H +0.029*I +0.0119*J +0.0*K +0.7005*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>102.1381</t>
+  </si>
+  <si>
+    <t>0.0209</t>
+  </si>
+  <si>
+    <t>-0.1439</t>
+  </si>
+  <si>
+    <t>-0.0137</t>
+  </si>
+  <si>
+    <t>-1.2405</t>
+  </si>
+  <si>
+    <t>0.0290</t>
+  </si>
+  <si>
+    <t>0.0119</t>
+  </si>
+  <si>
+    <t>0.7005</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0*B + 0.0*C -0.056*D +0.0449*E +0.0*F + 0.0*G +0.0688*H +0.0066*I +0.0001*J +0.0558*K -3.1359*L -43.1013*M</t>
+  </si>
+  <si>
+    <t>-0.0560</t>
+  </si>
+  <si>
+    <t>0.0449</t>
+  </si>
+  <si>
+    <t>0.0688</t>
+  </si>
+  <si>
+    <t>0.0066</t>
+  </si>
+  <si>
+    <t>0.0558</t>
+  </si>
+  <si>
+    <t>-3.1359</t>
+  </si>
+  <si>
+    <t>-43.1013</t>
+  </si>
+  <si>
+    <t>-267.8211 +0.0*B + 0.0*C +0.204*D -0.0538*E +0.0022*F + 0.0*G -0.3048*H +0.0217*I +0.0001*J +0.222*K -0.1367*L -41.7786*M</t>
+  </si>
+  <si>
+    <t>-267.8211</t>
+  </si>
+  <si>
+    <t>0.2040</t>
+  </si>
+  <si>
+    <t>-0.0538</t>
+  </si>
+  <si>
+    <t>0.0022</t>
+  </si>
+  <si>
+    <t>-0.3048</t>
+  </si>
+  <si>
+    <t>0.0217</t>
+  </si>
+  <si>
+    <t>0.2220</t>
+  </si>
+  <si>
+    <t>-0.1367</t>
+  </si>
+  <si>
+    <t>-41.7786</t>
+  </si>
+  <si>
+    <t>81.1954 +0.0112*B + 0.0*C -0.0702*D +0.0011*E +0.0057*F + 0.0*G -0.3254*H +0.004*I +0.028*J +0.0*K +1.8214*L -71.7186*M</t>
+  </si>
+  <si>
+    <t>81.1954</t>
+  </si>
+  <si>
+    <t>0.0112</t>
+  </si>
+  <si>
+    <t>-0.0702</t>
+  </si>
+  <si>
+    <t>0.0057</t>
+  </si>
+  <si>
+    <t>-0.3254</t>
+  </si>
+  <si>
+    <t>0.0040</t>
+  </si>
+  <si>
+    <t>0.0280</t>
+  </si>
+  <si>
+    <t>1.8214</t>
+  </si>
+  <si>
+    <t>-71.7186</t>
+  </si>
+  <si>
+    <t>-218.6027 +0.0169*B + 0.0*C +0.038*D -0.0243*E +0.017*F + 0.0*G -1.0492*H -0.0244*I +0.0179*J +0.1124*K -0.7853*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>-218.6027</t>
+  </si>
+  <si>
+    <t>0.0169</t>
+  </si>
+  <si>
+    <t>0.0380</t>
+  </si>
+  <si>
+    <t>-0.0243</t>
+  </si>
+  <si>
+    <t>0.0170</t>
+  </si>
+  <si>
+    <t>-1.0492</t>
+  </si>
+  <si>
+    <t>-0.0244</t>
+  </si>
+  <si>
+    <t>0.0179</t>
+  </si>
+  <si>
+    <t>0.1124</t>
+  </si>
+  <si>
+    <t>-0.7853</t>
+  </si>
+  <si>
+    <t>5.5955 +0.0201*B + 0.0*C +0.0808*D -0.0318*E +0.0*F + 0.0*G +0.4309*H +0.0028*I +0.0061*J +0.0798*K +1.0324*L -29.7501*M</t>
+  </si>
+  <si>
+    <t>5.5955</t>
+  </si>
+  <si>
+    <t>0.0201</t>
+  </si>
+  <si>
+    <t>0.0808</t>
+  </si>
+  <si>
+    <t>-0.0318</t>
+  </si>
+  <si>
+    <t>0.4309</t>
+  </si>
+  <si>
+    <t>0.0028</t>
+  </si>
+  <si>
+    <t>0.0061</t>
+  </si>
+  <si>
+    <t>0.0798</t>
+  </si>
+  <si>
+    <t>1.0324</t>
+  </si>
+  <si>
+    <t>-29.7501</t>
+  </si>
+  <si>
+    <t>122.703 +0.0053*B + 0.0*C -0.0232*D +0.0387*E +0.0831*F + 0.0*G +0.5099*H +0.0186*I +0.0067*J +0.1566*K -0.4323*L -1.5019*M</t>
+  </si>
+  <si>
+    <t>122.7030</t>
+  </si>
+  <si>
+    <t>-0.0232</t>
+  </si>
+  <si>
+    <t>0.0387</t>
+  </si>
+  <si>
+    <t>0.5099</t>
+  </si>
+  <si>
+    <t>0.0186</t>
+  </si>
+  <si>
+    <t>0.0067</t>
+  </si>
+  <si>
+    <t>0.1566</t>
+  </si>
+  <si>
+    <t>-0.4323</t>
+  </si>
+  <si>
+    <t>-1.5019</t>
+  </si>
+  <si>
+    <t>-208.0336 +0.0097*B + 0.0*C +0.0766*D -0.0314*E +0.164*F + 0.0*G -1.6614*H -0.0386*I +0.0221*J +0.1715*K +0.4295*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>-208.0336</t>
+  </si>
+  <si>
+    <t>0.0097</t>
+  </si>
+  <si>
+    <t>0.0766</t>
+  </si>
+  <si>
+    <t>-0.0314</t>
+  </si>
+  <si>
+    <t>0.1640</t>
+  </si>
+  <si>
+    <t>-1.6614</t>
+  </si>
+  <si>
+    <t>-0.0386</t>
+  </si>
+  <si>
+    <t>0.0221</t>
+  </si>
+  <si>
+    <t>0.1715</t>
+  </si>
+  <si>
+    <t>0.4295</t>
+  </si>
+  <si>
+    <t>-150.4579 +0.0*B + 0.0*C +0.0128*D -0.0263*E +0.0926*F + 0.0*G -0.6363*H -0.0298*I +0.002*J +0.12*K -0.6661*L -36.865*M</t>
+  </si>
+  <si>
+    <t>-150.4579</t>
+  </si>
+  <si>
+    <t>0.0128</t>
+  </si>
+  <si>
+    <t>-0.0263</t>
+  </si>
+  <si>
+    <t>0.0926</t>
+  </si>
+  <si>
+    <t>-0.6363</t>
+  </si>
+  <si>
+    <t>-0.0298</t>
+  </si>
+  <si>
+    <t>0.0020</t>
+  </si>
+  <si>
+    <t>0.1200</t>
+  </si>
+  <si>
+    <t>-0.6661</t>
+  </si>
+  <si>
+    <t>-36.8650</t>
+  </si>
+  <si>
+    <t>-25.4702 +0.0118*B + 0.0*C -0.0588*D -0.0187*E +0.0452*F + 0.0*G -2.1889*H -0.043*I +0.0001*J +0.0348*K +0.1406*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>-25.4702</t>
+  </si>
+  <si>
+    <t>-0.0588</t>
+  </si>
+  <si>
+    <t>-0.0187</t>
+  </si>
+  <si>
+    <t>0.0452</t>
+  </si>
+  <si>
+    <t>-2.1889</t>
+  </si>
+  <si>
+    <t>-0.0430</t>
+  </si>
+  <si>
+    <t>0.0348</t>
+  </si>
+  <si>
+    <t>0.1406</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0059*B + 0.0*C +0.0012*D -0.0382*E +0.0291*F + 0.0*G -0.8053*H -0.0037*I +0.0001*J +0.1345*K +1.2676*L -14.8565*M</t>
+  </si>
+  <si>
+    <t>0.0059</t>
+  </si>
+  <si>
+    <t>0.0012</t>
+  </si>
+  <si>
+    <t>-0.0382</t>
+  </si>
+  <si>
+    <t>0.0291</t>
+  </si>
+  <si>
+    <t>-0.8053</t>
+  </si>
+  <si>
+    <t>0.1345</t>
+  </si>
+  <si>
+    <t>1.2676</t>
+  </si>
+  <si>
+    <t>-14.8565</t>
+  </si>
+  <si>
+    <t>51.7025 +0.0183*B + 0.0*C -0.0458*D +0.0067*E +0.0311*F + 0.0*G -0.3443*H -0.0286*I +0.0067*J +0.1316*K +1.1924*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>51.7025</t>
+  </si>
+  <si>
+    <t>0.0183</t>
+  </si>
+  <si>
+    <t>-0.0458</t>
+  </si>
+  <si>
+    <t>0.0311</t>
+  </si>
+  <si>
+    <t>-0.3443</t>
+  </si>
+  <si>
+    <t>-0.0286</t>
+  </si>
+  <si>
+    <t>0.1316</t>
+  </si>
+  <si>
+    <t>1.1924</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0*B + 0.0*C +0.1107*D +0.0052*E +0.1703*F + 0.0*G -1.4254*H -0.0301*I +0.0001*J +0.0*K -0.6311*L -34.9189*M</t>
+  </si>
+  <si>
+    <t>0.1107</t>
+  </si>
+  <si>
+    <t>0.0052</t>
+  </si>
+  <si>
+    <t>-1.4254</t>
+  </si>
+  <si>
+    <t>-0.0301</t>
+  </si>
+  <si>
+    <t>-0.6311</t>
+  </si>
+  <si>
+    <t>-34.9189</t>
+  </si>
+  <si>
+    <t>-71.0309 +0.0133*B + 0.0*C +0.234*D +0.0333*E +0.0*F + 0.0*G -1.533*H +0.0001*I +0.0001*J +0.3128*K +0.9418*L -25.9745*M</t>
+  </si>
+  <si>
+    <t>-71.0309</t>
+  </si>
+  <si>
+    <t>0.0133</t>
+  </si>
+  <si>
+    <t>0.2340</t>
+  </si>
+  <si>
+    <t>0.0333</t>
+  </si>
+  <si>
+    <t>-1.5330</t>
+  </si>
+  <si>
+    <t>0.3128</t>
+  </si>
+  <si>
+    <t>0.9418</t>
+  </si>
+  <si>
+    <t>-25.9745</t>
+  </si>
+  <si>
+    <t>-981.1021 +0.028*B + 0.0*C -0.0106*D +0.0438*E +0.0*F + 0.0*G -1.1761*H -0.0109*I +0.007*J +0.0027*K +0.4284*L -44.435*M</t>
+  </si>
+  <si>
+    <t>-981.1021</t>
+  </si>
+  <si>
+    <t>-0.0106</t>
+  </si>
+  <si>
+    <t>0.0438</t>
+  </si>
+  <si>
+    <t>-1.1761</t>
+  </si>
+  <si>
+    <t>-0.0109</t>
+  </si>
+  <si>
+    <t>0.0070</t>
+  </si>
+  <si>
+    <t>0.0027</t>
+  </si>
+  <si>
+    <t>0.4284</t>
+  </si>
+  <si>
+    <t>-44.4350</t>
+  </si>
+  <si>
+    <t>-214.0094 +0.01*B + 0.0*C +0.0667*D +0.0246*E +0.0*F + 0.0*G -2.2916*H +0.018*I +0.0109*J +0.0*K +1.2846*L -7.9333*M</t>
+  </si>
+  <si>
+    <t>-214.0094</t>
+  </si>
+  <si>
+    <t>0.0100</t>
+  </si>
+  <si>
+    <t>0.0667</t>
+  </si>
+  <si>
+    <t>0.0246</t>
+  </si>
+  <si>
+    <t>-2.2916</t>
+  </si>
+  <si>
+    <t>1.2846</t>
+  </si>
+  <si>
+    <t>-7.9333</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0092*B + 0.0*C +0.2566*D +0.0628*E +0.0144*F + 0.0*G +0.6986*H +0.0036*I +0.025*J +0.0*K +0.4867*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>0.0092</t>
+  </si>
+  <si>
+    <t>0.2566</t>
+  </si>
+  <si>
+    <t>0.0628</t>
+  </si>
+  <si>
+    <t>0.0144</t>
+  </si>
+  <si>
+    <t>0.6986</t>
+  </si>
+  <si>
+    <t>0.0036</t>
+  </si>
+  <si>
+    <t>0.0250</t>
+  </si>
+  <si>
+    <t>0.4867</t>
+  </si>
+  <si>
+    <t>-1003.3737 +0.0*B + 0.0*C -0.247*D -0.0113*E +0.0762*F + 0.0*G +0.8226*H -0.0093*I +0.0285*J +0.0*K -1.7173*L -13.2151*M</t>
+  </si>
+  <si>
+    <t>-1003.3737</t>
+  </si>
+  <si>
+    <t>-0.2470</t>
+  </si>
+  <si>
+    <t>-0.0113</t>
+  </si>
+  <si>
+    <t>0.0762</t>
+  </si>
+  <si>
+    <t>-0.0093</t>
+  </si>
+  <si>
+    <t>0.0285</t>
+  </si>
+  <si>
+    <t>-1.7173</t>
+  </si>
+  <si>
+    <t>-13.2151</t>
+  </si>
+  <si>
+    <t>43.0848 +0.0078*B + 0.0*C -0.2505*D -0.0047*E +0.0*F + 0.0*G +0.3383*H -0.0027*I +0.0001*J +0.0*K -1.1232*L -13.4351*M</t>
+  </si>
+  <si>
+    <t>43.0848</t>
+  </si>
+  <si>
+    <t>0.0078</t>
+  </si>
+  <si>
+    <t>-0.2505</t>
+  </si>
+  <si>
+    <t>-0.0047</t>
+  </si>
+  <si>
+    <t>0.3383</t>
+  </si>
+  <si>
+    <t>-0.0027</t>
+  </si>
+  <si>
+    <t>-1.1232</t>
+  </si>
+  <si>
+    <t>-13.4351</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0*B + 0.0*C +0.0654*D -0.0209*E +0.0*F + 0.0*G -0.5886*H -0.0345*I +0.0001*J +0.0*K +1.6661*L -10.4138*M</t>
+  </si>
+  <si>
+    <t>0.0654</t>
+  </si>
+  <si>
+    <t>-0.0209</t>
+  </si>
+  <si>
+    <t>-0.5886</t>
+  </si>
+  <si>
+    <t>1.6661</t>
+  </si>
+  <si>
+    <t>-10.4138</t>
+  </si>
+  <si>
+    <t>-486.1945 +0.0114*B + 0.0*C -0.0103*D -0.0096*E +0.0696*F + 0.0*G +0.4431*H -0.0231*I +0.0001*J +0.0265*K -2.2694*L -58.2414*M</t>
+  </si>
+  <si>
+    <t>-486.1945</t>
+  </si>
+  <si>
+    <t>0.0114</t>
+  </si>
+  <si>
+    <t>-0.0103</t>
+  </si>
+  <si>
+    <t>0.0696</t>
+  </si>
+  <si>
+    <t>0.4431</t>
+  </si>
+  <si>
+    <t>-0.0231</t>
+  </si>
+  <si>
+    <t>0.0265</t>
+  </si>
+  <si>
+    <t>-2.2694</t>
+  </si>
+  <si>
+    <t>-58.2414</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0323*B + 0.0*C -0.0271*D +0.0196*E +0.0502*F + 0.0*G +0.8226*H +0.0144*I +0.0046*J +0.0*K -1.6279*L -5.2252*M</t>
+  </si>
+  <si>
+    <t>0.0323</t>
+  </si>
+  <si>
+    <t>-0.0271</t>
+  </si>
+  <si>
+    <t>0.0196</t>
+  </si>
+  <si>
+    <t>0.0502</t>
+  </si>
+  <si>
+    <t>0.0046</t>
+  </si>
+  <si>
+    <t>-1.6279</t>
+  </si>
+  <si>
+    <t>-5.2252</t>
+  </si>
+  <si>
+    <t>-513.8479 +0.0*B + 0.0*C -0.0759*D -0.0411*E +0.1381*F + 0.0*G +0.5912*H -0.0112*I +0.0265*J +0.0744*K -0.9406*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>-513.8479</t>
+  </si>
+  <si>
+    <t>-0.0759</t>
+  </si>
+  <si>
+    <t>-0.0411</t>
+  </si>
+  <si>
+    <t>0.1381</t>
+  </si>
+  <si>
+    <t>0.5912</t>
+  </si>
+  <si>
+    <t>-0.0112</t>
+  </si>
+  <si>
+    <t>0.0744</t>
+  </si>
+  <si>
+    <t>-0.9406</t>
+  </si>
+  <si>
+    <t>118.7046 +0.0*B + 0.0*C -0.0199*D -0.0335*E +0.0*F + 0.0*G +0.6444*H +0.0323*I +0.0001*J +0.1404*K -0.7463*L -26.5282*M</t>
+  </si>
+  <si>
+    <t>118.7046</t>
+  </si>
+  <si>
+    <t>-0.0335</t>
+  </si>
+  <si>
+    <t>0.6444</t>
+  </si>
+  <si>
+    <t>0.1404</t>
+  </si>
+  <si>
+    <t>-0.7463</t>
+  </si>
+  <si>
+    <t>-26.5282</t>
+  </si>
+  <si>
+    <t>-433.7781 +0.0*B + 0.0*C +0.0095*D -0.0319*E +0.0476*F + 0.0*G -0.5208*H -0.0164*I +0.0001*J +0.0*K +0.5506*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>-433.7781</t>
+  </si>
+  <si>
+    <t>0.0095</t>
+  </si>
+  <si>
+    <t>-0.0319</t>
+  </si>
+  <si>
+    <t>0.0476</t>
+  </si>
+  <si>
+    <t>-0.5208</t>
+  </si>
+  <si>
+    <t>-0.0164</t>
+  </si>
+  <si>
+    <t>0.5506</t>
+  </si>
+  <si>
+    <t>-621.8752 +0.0097*B + 0.0*C +0.0958*D -0.0626*E +0.065*F + 0.0*G -1.2516*H +0.0019*I +0.0001*J +0.0*K -1.6474*L -10.0183*M</t>
+  </si>
+  <si>
+    <t>-621.8752</t>
+  </si>
+  <si>
+    <t>0.0958</t>
+  </si>
+  <si>
+    <t>-0.0626</t>
+  </si>
+  <si>
+    <t>0.0650</t>
+  </si>
+  <si>
+    <t>-1.2516</t>
+  </si>
+  <si>
+    <t>0.0019</t>
+  </si>
+  <si>
+    <t>-1.6474</t>
+  </si>
+  <si>
+    <t>-10.0183</t>
+  </si>
+  <si>
+    <t>-17.6392 +0.0*B + 0.0*C +0.0819*D -0.0623*E +0.0261*F + 0.0*G -1.906*H -0.0258*I +0.007*J +0.0*K -0.5009*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>-17.6392</t>
+  </si>
+  <si>
+    <t>0.0819</t>
+  </si>
+  <si>
+    <t>-0.0623</t>
+  </si>
+  <si>
+    <t>0.0261</t>
+  </si>
+  <si>
+    <t>-1.9060</t>
+  </si>
+  <si>
+    <t>-0.0258</t>
+  </si>
+  <si>
+    <t>-0.5009</t>
+  </si>
+  <si>
+    <t>-426.2075 +0.0205*B + 0.0*C -0.1353*D +0.0179*E +0.1224*F + 0.0*G -3.4104*H -0.0291*I +0.0142*J +0.0362*K +0.1962*L -30.133*M</t>
+  </si>
+  <si>
+    <t>-426.2075</t>
+  </si>
+  <si>
+    <t>0.0205</t>
+  </si>
+  <si>
+    <t>-0.1353</t>
+  </si>
+  <si>
+    <t>0.1224</t>
+  </si>
+  <si>
+    <t>-3.4104</t>
+  </si>
+  <si>
+    <t>-0.0291</t>
+  </si>
+  <si>
+    <t>0.0142</t>
+  </si>
+  <si>
+    <t>0.0362</t>
+  </si>
+  <si>
+    <t>0.1962</t>
+  </si>
+  <si>
+    <t>-30.1330</t>
+  </si>
+  <si>
+    <t>-102.1902 +0.006*B + 0.0*C +0.147*D +0.0078*E +0.0519*F + 0.0*G -0.9524*H -0.0221*I +0.0005*J +0.1175*K -0.5345*L -2.5627*M</t>
+  </si>
+  <si>
+    <t>-102.1902</t>
+  </si>
+  <si>
+    <t>0.0060</t>
+  </si>
+  <si>
+    <t>0.1470</t>
+  </si>
+  <si>
+    <t>0.0519</t>
+  </si>
+  <si>
+    <t>-0.9524</t>
+  </si>
+  <si>
+    <t>-0.0221</t>
+  </si>
+  <si>
+    <t>0.0005</t>
+  </si>
+  <si>
+    <t>0.1175</t>
+  </si>
+  <si>
+    <t>-0.5345</t>
+  </si>
+  <si>
+    <t>-2.5627</t>
+  </si>
+  <si>
+    <t>140.3236 +0.021*B + 0.0*C -0.0365*D +0.0425*E +0.0043*F + 0.0*G -2.893*H -0.0339*I +0.0001*J +0.0161*K -0.1292*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>0.0210</t>
+  </si>
+  <si>
+    <t>-0.0365</t>
+  </si>
+  <si>
+    <t>0.0425</t>
+  </si>
+  <si>
+    <t>0.0043</t>
+  </si>
+  <si>
+    <t>-2.8930</t>
+  </si>
+  <si>
+    <t>-0.0339</t>
+  </si>
+  <si>
+    <t>0.0161</t>
+  </si>
+  <si>
+    <t>-0.1292</t>
+  </si>
+  <si>
+    <t>15.1809 +0.0051*B + 0.0*C +0.1054*D -0.0824*E +0.0454*F + 0.0*G +0.4591*H -0.0446*I +0.0219*J +0.1099*K -0.5292*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>15.1809</t>
+  </si>
+  <si>
+    <t>0.0051</t>
+  </si>
+  <si>
+    <t>0.1054</t>
+  </si>
+  <si>
+    <t>-0.0824</t>
+  </si>
+  <si>
+    <t>0.0454</t>
+  </si>
+  <si>
+    <t>0.4591</t>
+  </si>
+  <si>
+    <t>-0.0446</t>
+  </si>
+  <si>
+    <t>0.0219</t>
+  </si>
+  <si>
+    <t>0.1099</t>
+  </si>
+  <si>
+    <t>-0.5292</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0109*B + 0.0*C +0.034*D -0.0183*E +0.0*F + 0.0*G +0.53*H -0.0305*I +0.0074*J +0.0*K +0.2957*L -1.2089*M</t>
+  </si>
+  <si>
+    <t>-0.0183</t>
+  </si>
+  <si>
+    <t>0.5300</t>
+  </si>
+  <si>
+    <t>-0.0305</t>
+  </si>
+  <si>
+    <t>0.2957</t>
+  </si>
+  <si>
+    <t>-1.2089</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0008*B + 0.0*C -0.0296*D -0.0373*E +0.0019*F + 0.0*G -0.0106*H +0.0062*I +0.0001*J +0.1821*K +1.1043*L +1.2519*M</t>
+  </si>
+  <si>
+    <t>0.0008</t>
+  </si>
+  <si>
+    <t>-0.0296</t>
+  </si>
+  <si>
+    <t>-0.0373</t>
+  </si>
+  <si>
+    <t>0.1821</t>
+  </si>
+  <si>
+    <t>1.1043</t>
+  </si>
+  <si>
+    <t>1.2519</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0*B + 0.0*C -0.1494*D -0.0666*E +0.1259*F + 0.0*G +0.32*H -0.0123*I +0.0102*J +0.0*K +2.1098*L -7.5154*M</t>
+  </si>
+  <si>
+    <t>-0.1494</t>
+  </si>
+  <si>
+    <t>-0.0666</t>
+  </si>
+  <si>
+    <t>0.1259</t>
+  </si>
+  <si>
+    <t>0.3200</t>
+  </si>
+  <si>
+    <t>-0.0123</t>
+  </si>
+  <si>
+    <t>0.0102</t>
+  </si>
+  <si>
+    <t>2.1098</t>
+  </si>
+  <si>
+    <t>-7.5154</t>
+  </si>
+  <si>
+    <t>-91.0531 +0.0189*B + 0.0*C +0.0626*D +0.0067*E +0.0*F + 0.0*G +0.1018*H +0.0317*I +0.0247*J +0.2804*K -0.6177*L -42.0284*M</t>
+  </si>
+  <si>
+    <t>-91.0531</t>
+  </si>
+  <si>
+    <t>0.0189</t>
+  </si>
+  <si>
+    <t>0.0626</t>
+  </si>
+  <si>
+    <t>0.1018</t>
+  </si>
+  <si>
+    <t>0.0247</t>
+  </si>
+  <si>
+    <t>0.2804</t>
+  </si>
+  <si>
+    <t>-0.6177</t>
+  </si>
+  <si>
+    <t>-42.0284</t>
+  </si>
+  <si>
+    <t>-205.9063 +0.0091*B + 0.0*C +0.1379*D -0.0634*E +0.1281*F + 0.0*G -0.6494*H -0.0207*I +0.0001*J +0.0*K +0.6131*L -9.2399*M</t>
+  </si>
+  <si>
+    <t>-205.9063</t>
+  </si>
+  <si>
+    <t>0.0091</t>
+  </si>
+  <si>
+    <t>0.1379</t>
+  </si>
+  <si>
+    <t>0.1281</t>
+  </si>
+  <si>
+    <t>-0.6494</t>
+  </si>
+  <si>
+    <t>-0.0207</t>
+  </si>
+  <si>
+    <t>0.6131</t>
+  </si>
+  <si>
+    <t>-9.2399</t>
+  </si>
+  <si>
+    <t>-774.4414 +0.0*B + 0.0*C -0.0377*D +0.0596*E +0.0137*F + 0.0*G -2.2546*H -0.0166*I +0.0027*J +0.0*K -0.1962*L -18.6253*M</t>
+  </si>
+  <si>
+    <t>-774.4414</t>
+  </si>
+  <si>
+    <t>-0.0377</t>
+  </si>
+  <si>
+    <t>0.0596</t>
+  </si>
+  <si>
+    <t>0.0137</t>
+  </si>
+  <si>
+    <t>-2.2546</t>
+  </si>
+  <si>
+    <t>-0.0166</t>
+  </si>
+  <si>
+    <t>-0.1962</t>
+  </si>
+  <si>
+    <t>-18.6253</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0353*B + 0.0*C +0.1419*D -0.0113*E +0.0*F + 0.0*G +0.8226*H -0.0097*I +0.0066*J +0.0606*K +0.0366*L -15.9547*M</t>
+  </si>
+  <si>
+    <t>0.0353</t>
+  </si>
+  <si>
+    <t>0.1419</t>
+  </si>
+  <si>
+    <t>-0.0097</t>
+  </si>
+  <si>
+    <t>0.0606</t>
+  </si>
+  <si>
+    <t>0.0366</t>
+  </si>
+  <si>
+    <t>-15.9547</t>
+  </si>
+  <si>
+    <t>-424.6302 +0.0003*B + 0.0*C -0.0005*D -0.0214*E +0.0*F + 0.0*G -0.3338*H -0.0168*I +0.0269*J +0.0*K +0.8607*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>-424.6302</t>
+  </si>
+  <si>
+    <t>0.0003</t>
+  </si>
+  <si>
+    <t>-0.0005</t>
+  </si>
+  <si>
+    <t>-0.0214</t>
+  </si>
+  <si>
+    <t>-0.3338</t>
+  </si>
+  <si>
+    <t>-0.0168</t>
+  </si>
+  <si>
+    <t>0.0269</t>
+  </si>
+  <si>
+    <t>0.8607</t>
+  </si>
+  <si>
+    <t>-1157.0363 +0.0032*B + 0.0*C -0.0421*D -0.053*E +0.0*F + 0.0*G -1.7861*H +0.0287*I +0.0191*J +0.2367*K +0.5195*L -46.33*M</t>
+  </si>
+  <si>
+    <t>-1157.0363</t>
+  </si>
+  <si>
+    <t>0.0032</t>
+  </si>
+  <si>
+    <t>-0.0421</t>
+  </si>
+  <si>
+    <t>-0.0530</t>
+  </si>
+  <si>
+    <t>-1.7861</t>
+  </si>
+  <si>
+    <t>0.0287</t>
+  </si>
+  <si>
+    <t>0.0191</t>
+  </si>
+  <si>
+    <t>0.2367</t>
+  </si>
+  <si>
+    <t>0.5195</t>
+  </si>
+  <si>
+    <t>-46.3300</t>
+  </si>
+  <si>
+    <t>-400.6314 +0.0154*B + 0.0*C -0.1466*D +0.0246*E +0.015*F + 0.0*G -0.9081*H +0.0051*I +0.0124*J +0.0148*K +0.9232*L -44.8497*M</t>
+  </si>
+  <si>
+    <t>-400.6314</t>
+  </si>
+  <si>
+    <t>-0.1466</t>
+  </si>
+  <si>
+    <t>0.0150</t>
+  </si>
+  <si>
+    <t>-0.9081</t>
+  </si>
+  <si>
+    <t>0.0124</t>
+  </si>
+  <si>
+    <t>0.0148</t>
+  </si>
+  <si>
+    <t>0.9232</t>
+  </si>
+  <si>
+    <t>-44.8497</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0169*B + 0.0*C -0.0345*D +0.0105*E +0.0*F + 0.0*G +0.6418*H -0.0152*I +0.0001*J +0.2065*K -0.7958*L -54.9491*M</t>
+  </si>
+  <si>
+    <t>0.0105</t>
+  </si>
+  <si>
+    <t>0.6418</t>
+  </si>
+  <si>
+    <t>0.2065</t>
+  </si>
+  <si>
+    <t>-0.7958</t>
+  </si>
+  <si>
+    <t>-54.9491</t>
+  </si>
+  <si>
+    <t>-904.6713 +0.0171*B + 0.0*C -0.1538*D +0.0627*E +0.0*F + 0.0*G +0.8226*H -0.0062*I +0.0051*J +0.0*K +0.222*L -12.6625*M</t>
+  </si>
+  <si>
+    <t>-904.6713</t>
+  </si>
+  <si>
+    <t>-0.1538</t>
+  </si>
+  <si>
+    <t>0.0627</t>
+  </si>
+  <si>
+    <t>-0.0062</t>
+  </si>
+  <si>
+    <t>-12.6625</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0099*B + 0.0*C +0.022*D -0.0148*E +0.0267*F + 0.0*G -0.0935*H -0.0498*I +0.0001*J +0.1649*K +0.0115*L -17.177*M</t>
+  </si>
+  <si>
+    <t>0.0099</t>
+  </si>
+  <si>
+    <t>0.0220</t>
+  </si>
+  <si>
+    <t>-0.0148</t>
+  </si>
+  <si>
+    <t>0.0267</t>
+  </si>
+  <si>
+    <t>-0.0935</t>
+  </si>
+  <si>
+    <t>-0.0498</t>
+  </si>
+  <si>
+    <t>0.1649</t>
+  </si>
+  <si>
+    <t>0.0115</t>
+  </si>
+  <si>
+    <t>-17.1770</t>
+  </si>
+  <si>
+    <t>-135.4747 +0.0133*B + 0.0*C -0.0628*D -0.03*E +0.0428*F + 0.0*G -1.6284*H -0.0018*I +0.0001*J +0.2038*K +0.2898*L -3.6037*M</t>
+  </si>
+  <si>
+    <t>-135.4747</t>
+  </si>
+  <si>
+    <t>-0.0628</t>
+  </si>
+  <si>
+    <t>-0.0300</t>
+  </si>
+  <si>
+    <t>0.0428</t>
+  </si>
+  <si>
+    <t>-1.6284</t>
+  </si>
+  <si>
+    <t>-0.0018</t>
+  </si>
+  <si>
+    <t>0.2038</t>
+  </si>
+  <si>
+    <t>0.2898</t>
+  </si>
+  <si>
+    <t>-3.6037</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0326*B + 0.0*C +0.1281*D -0.0688*E +0.0*F + 0.0*G -1.2065*H -0.0104*I +0.0134*J +0.0*K +0.0261*L -34.8032*M</t>
+  </si>
+  <si>
+    <t>0.0326</t>
+  </si>
+  <si>
+    <t>-0.0688</t>
+  </si>
+  <si>
+    <t>-1.2065</t>
+  </si>
+  <si>
+    <t>-0.0104</t>
+  </si>
+  <si>
+    <t>0.0134</t>
+  </si>
+  <si>
+    <t>-34.8032</t>
+  </si>
+  <si>
+    <t>-443.1174 +0.0*B + 0.0*C -0.1099*D -0.0509*E +0.0*F + 0.0*G +0.7965*H -0.0326*I +0.0422*J +0.1309*K +0.0243*L -37.9797*M</t>
+  </si>
+  <si>
+    <t>-443.1174</t>
+  </si>
+  <si>
+    <t>-0.1099</t>
+  </si>
+  <si>
+    <t>-0.0509</t>
+  </si>
+  <si>
+    <t>0.7965</t>
+  </si>
+  <si>
+    <t>-0.0326</t>
+  </si>
+  <si>
+    <t>0.0422</t>
+  </si>
+  <si>
+    <t>0.1309</t>
+  </si>
+  <si>
+    <t>0.0243</t>
+  </si>
+  <si>
+    <t>-37.9797</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0*B + 0.0*C +0.0185*D +0.0922*E +0.0242*F + 0.0*G +0.8226*H -0.027*I +0.0059*J +0.3046*K -0.7245*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>0.0185</t>
+  </si>
+  <si>
+    <t>0.0922</t>
+  </si>
+  <si>
+    <t>0.0242</t>
+  </si>
+  <si>
+    <t>-0.0270</t>
+  </si>
+  <si>
+    <t>0.3046</t>
+  </si>
+  <si>
+    <t>-0.7245</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0*B + 0.0*C +0.0812*D +0.0341*E +0.0701*F + 0.0*G -2.3347*H -0.0275*I +0.003*J +0.0537*K +0.4264*L -6.0199*M</t>
+  </si>
+  <si>
+    <t>0.0812</t>
+  </si>
+  <si>
+    <t>0.0341</t>
+  </si>
+  <si>
+    <t>0.0701</t>
+  </si>
+  <si>
+    <t>-2.3347</t>
+  </si>
+  <si>
+    <t>-0.0275</t>
+  </si>
+  <si>
+    <t>0.0030</t>
+  </si>
+  <si>
+    <t>0.0537</t>
+  </si>
+  <si>
+    <t>0.4264</t>
+  </si>
+  <si>
+    <t>-6.0199</t>
+  </si>
+  <si>
+    <t>-796.6048 +0.0138*B + 0.0*C +0.0785*D +0.019*E +0.0994*F + 0.0*G +0.5343*H -0.0006*I +0.0054*J +0.0*K +0.2501*L -5.0949*M</t>
+  </si>
+  <si>
+    <t>-796.6048</t>
+  </si>
+  <si>
+    <t>0.0138</t>
+  </si>
+  <si>
+    <t>0.0785</t>
+  </si>
+  <si>
+    <t>0.0994</t>
+  </si>
+  <si>
+    <t>0.5343</t>
+  </si>
+  <si>
+    <t>-0.0006</t>
+  </si>
+  <si>
+    <t>0.0054</t>
+  </si>
+  <si>
+    <t>0.2501</t>
+  </si>
+  <si>
+    <t>-5.0949</t>
+  </si>
+  <si>
+    <t>-11.8491 +0.0*B + 0.0*C -0.1293*D +0.0371*E +0.0278*F + 0.0*G +0.3524*H -0.0104*I +0.0068*J +0.1914*K -0.6221*L -8.5365*M</t>
+  </si>
+  <si>
+    <t>-11.8491</t>
+  </si>
+  <si>
+    <t>-0.1293</t>
+  </si>
+  <si>
+    <t>0.0371</t>
+  </si>
+  <si>
+    <t>0.0278</t>
+  </si>
+  <si>
+    <t>0.3524</t>
+  </si>
+  <si>
+    <t>0.0068</t>
+  </si>
+  <si>
+    <t>0.1914</t>
+  </si>
+  <si>
+    <t>-0.6221</t>
+  </si>
+  <si>
+    <t>-8.5365</t>
+  </si>
+  <si>
+    <t>-370.2335 +0.0019*B + 0.0*C -0.0345*D +0.0067*E +0.0*F + 0.0*G +0.8226*H -0.0313*I +0.0038*J +0.0041*K +1.1885*L -5.4384*M</t>
+  </si>
+  <si>
+    <t>-370.2335</t>
+  </si>
+  <si>
+    <t>-0.0313</t>
+  </si>
+  <si>
+    <t>0.0038</t>
+  </si>
+  <si>
+    <t>0.0041</t>
+  </si>
+  <si>
+    <t>1.1885</t>
+  </si>
+  <si>
+    <t>-5.4384</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0*B + 0.0*C +0.0363*D +0.0311*E +0.0356*F + 0.0*G +0.8106*H -0.0228*I +0.0256*J +0.3764*K -0.4808*L -25.2442*M</t>
+  </si>
+  <si>
+    <t>0.0363</t>
+  </si>
+  <si>
+    <t>0.0356</t>
+  </si>
+  <si>
+    <t>0.8106</t>
+  </si>
+  <si>
+    <t>0.0256</t>
+  </si>
+  <si>
+    <t>0.3764</t>
+  </si>
+  <si>
+    <t>-0.4808</t>
+  </si>
+  <si>
+    <t>-25.2442</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0313*B + 0.0*C -0.0607*D -0.0169*E +0.0123*F + 0.0*G -2.0652*H -0.0319*I +0.0001*J +0.0*K -0.1781*L -4.2766*M</t>
+  </si>
+  <si>
+    <t>0.0313</t>
+  </si>
+  <si>
+    <t>-0.0607</t>
+  </si>
+  <si>
+    <t>-0.0169</t>
+  </si>
+  <si>
+    <t>0.0123</t>
+  </si>
+  <si>
+    <t>-2.0652</t>
+  </si>
+  <si>
+    <t>-0.1781</t>
+  </si>
+  <si>
+    <t>-4.2766</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0*B + 0.0*C +0.1244*D -0.0093*E +0.0272*F + 0.0*G +0.3444*H -0.0365*I +0.0116*J +0.0865*K +0.3081*L -2.5814*M</t>
+  </si>
+  <si>
+    <t>0.1244</t>
+  </si>
+  <si>
+    <t>0.0272</t>
+  </si>
+  <si>
+    <t>0.3444</t>
+  </si>
+  <si>
+    <t>0.0116</t>
+  </si>
+  <si>
+    <t>0.0865</t>
+  </si>
+  <si>
+    <t>0.3081</t>
+  </si>
+  <si>
+    <t>-2.5814</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0*B + 0.0*C -0.0617*D -0.0243*E +0.0*F + 0.0*G -1.2215*H +0.016*I +0.0257*J +0.0*K -0.9139*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>-0.0617</t>
+  </si>
+  <si>
+    <t>-1.2215</t>
+  </si>
+  <si>
+    <t>0.0160</t>
+  </si>
+  <si>
+    <t>0.0257</t>
+  </si>
+  <si>
+    <t>-0.9139</t>
+  </si>
+  <si>
+    <t>-414.1603 +0.0175*B + 0.0*C +0.0284*D -0.0569*E +0.1292*F + 0.0*G +0.8226*H -0.0249*I +0.0011*J +0.1027*K +0.1624*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>-414.1603</t>
+  </si>
+  <si>
+    <t>0.0175</t>
+  </si>
+  <si>
+    <t>0.0284</t>
+  </si>
+  <si>
+    <t>-0.0569</t>
+  </si>
+  <si>
+    <t>0.1292</t>
+  </si>
+  <si>
+    <t>-0.0249</t>
+  </si>
+  <si>
+    <t>0.1027</t>
+  </si>
+  <si>
+    <t>0.1624</t>
+  </si>
+  <si>
+    <t>140.3236 +0.0057*B + 0.0*C -0.0946*D -0.0519*E +0.0*F + 0.0*G -0.5004*H +0.0297*I +0.0001*J +0.0943*K -0.1613*L +1.5113*M</t>
+  </si>
+  <si>
+    <t>-0.0946</t>
+  </si>
+  <si>
+    <t>-0.0519</t>
+  </si>
+  <si>
+    <t>-0.5004</t>
+  </si>
+  <si>
+    <t>0.0297</t>
+  </si>
+  <si>
+    <t>0.0943</t>
+  </si>
+  <si>
+    <t>-0.1613</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -649,140 +2828,141 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -808,6 +2988,7 @@
     <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="42" xr:uid="{C2BA48F6-AEC7-485E-9CB8-E98232AC6CE9}"/>
     <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
@@ -1136,7 +3317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7F1A0C-4A91-4B8A-BD36-CA9C73539D24}">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
@@ -3066,8 +5247,3768 @@
         <v>-26.7789</v>
       </c>
     </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42" t="s">
+        <v>59</v>
+      </c>
+      <c r="G42" t="s">
+        <v>60</v>
+      </c>
+      <c r="H42" t="s">
+        <v>61</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42" t="s">
+        <v>62</v>
+      </c>
+      <c r="K42" t="s">
+        <v>63</v>
+      </c>
+      <c r="L42" t="s">
+        <v>64</v>
+      </c>
+      <c r="M42" t="s">
+        <v>58</v>
+      </c>
+      <c r="N42" t="s">
+        <v>65</v>
+      </c>
+      <c r="O42" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43" t="s">
+        <v>70</v>
+      </c>
+      <c r="G43" t="s">
+        <v>71</v>
+      </c>
+      <c r="H43" t="s">
+        <v>58</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43" t="s">
+        <v>72</v>
+      </c>
+      <c r="K43" t="s">
+        <v>73</v>
+      </c>
+      <c r="L43" t="s">
+        <v>74</v>
+      </c>
+      <c r="M43" t="s">
+        <v>58</v>
+      </c>
+      <c r="N43" t="s">
+        <v>75</v>
+      </c>
+      <c r="O43" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" t="s">
+        <v>78</v>
+      </c>
+      <c r="D44" t="s">
+        <v>58</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44" t="s">
+        <v>79</v>
+      </c>
+      <c r="G44" t="s">
+        <v>80</v>
+      </c>
+      <c r="H44" t="s">
+        <v>58</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44" t="s">
+        <v>81</v>
+      </c>
+      <c r="K44" t="s">
+        <v>82</v>
+      </c>
+      <c r="L44" t="s">
+        <v>83</v>
+      </c>
+      <c r="M44" t="s">
+        <v>58</v>
+      </c>
+      <c r="N44" t="s">
+        <v>84</v>
+      </c>
+      <c r="O44" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" t="s">
+        <v>88</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45" t="s">
+        <v>89</v>
+      </c>
+      <c r="G45" t="s">
+        <v>57</v>
+      </c>
+      <c r="H45" t="s">
+        <v>58</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45" t="s">
+        <v>90</v>
+      </c>
+      <c r="K45" t="s">
+        <v>91</v>
+      </c>
+      <c r="L45" t="s">
+        <v>92</v>
+      </c>
+      <c r="M45" t="s">
+        <v>93</v>
+      </c>
+      <c r="N45" t="s">
+        <v>94</v>
+      </c>
+      <c r="O45" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46" t="s">
+        <v>98</v>
+      </c>
+      <c r="G46" t="s">
+        <v>99</v>
+      </c>
+      <c r="H46" t="s">
+        <v>100</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46" t="s">
+        <v>101</v>
+      </c>
+      <c r="K46" t="s">
+        <v>102</v>
+      </c>
+      <c r="L46" t="s">
+        <v>103</v>
+      </c>
+      <c r="M46" t="s">
+        <v>58</v>
+      </c>
+      <c r="N46" t="s">
+        <v>104</v>
+      </c>
+      <c r="O46" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>106</v>
+      </c>
+      <c r="C47" t="s">
+        <v>107</v>
+      </c>
+      <c r="D47" t="s">
+        <v>58</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47" t="s">
+        <v>108</v>
+      </c>
+      <c r="G47" t="s">
+        <v>109</v>
+      </c>
+      <c r="H47" t="s">
+        <v>110</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47" t="s">
+        <v>111</v>
+      </c>
+      <c r="K47" t="s">
+        <v>112</v>
+      </c>
+      <c r="L47" t="s">
+        <v>74</v>
+      </c>
+      <c r="M47" t="s">
+        <v>58</v>
+      </c>
+      <c r="N47" t="s">
+        <v>113</v>
+      </c>
+      <c r="O47" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>114</v>
+      </c>
+      <c r="C48" t="s">
+        <v>115</v>
+      </c>
+      <c r="D48" t="s">
+        <v>116</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48" t="s">
+        <v>117</v>
+      </c>
+      <c r="G48" t="s">
+        <v>118</v>
+      </c>
+      <c r="H48" t="s">
+        <v>119</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48" t="s">
+        <v>120</v>
+      </c>
+      <c r="K48" t="s">
+        <v>121</v>
+      </c>
+      <c r="L48" t="s">
+        <v>122</v>
+      </c>
+      <c r="M48" t="s">
+        <v>58</v>
+      </c>
+      <c r="N48" t="s">
+        <v>123</v>
+      </c>
+      <c r="O48" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>125</v>
+      </c>
+      <c r="C49" t="s">
+        <v>126</v>
+      </c>
+      <c r="D49" t="s">
+        <v>127</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49" t="s">
+        <v>128</v>
+      </c>
+      <c r="G49" t="s">
+        <v>129</v>
+      </c>
+      <c r="H49" t="s">
+        <v>130</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49" t="s">
+        <v>120</v>
+      </c>
+      <c r="K49" t="s">
+        <v>131</v>
+      </c>
+      <c r="L49" t="s">
+        <v>74</v>
+      </c>
+      <c r="M49" t="s">
+        <v>58</v>
+      </c>
+      <c r="N49" t="s">
+        <v>132</v>
+      </c>
+      <c r="O49" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" t="s">
+        <v>135</v>
+      </c>
+      <c r="D50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50" t="s">
+        <v>61</v>
+      </c>
+      <c r="G50" t="s">
+        <v>137</v>
+      </c>
+      <c r="H50" t="s">
+        <v>58</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50" t="s">
+        <v>138</v>
+      </c>
+      <c r="K50" t="s">
+        <v>139</v>
+      </c>
+      <c r="L50" t="s">
+        <v>74</v>
+      </c>
+      <c r="M50" t="s">
+        <v>140</v>
+      </c>
+      <c r="N50" t="s">
+        <v>141</v>
+      </c>
+      <c r="O50" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>143</v>
+      </c>
+      <c r="C51" t="s">
+        <v>144</v>
+      </c>
+      <c r="D51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51" t="s">
+        <v>145</v>
+      </c>
+      <c r="G51" t="s">
+        <v>146</v>
+      </c>
+      <c r="H51" t="s">
+        <v>58</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51" t="s">
+        <v>147</v>
+      </c>
+      <c r="K51" t="s">
+        <v>148</v>
+      </c>
+      <c r="L51" t="s">
+        <v>149</v>
+      </c>
+      <c r="M51" t="s">
+        <v>150</v>
+      </c>
+      <c r="N51" t="s">
+        <v>151</v>
+      </c>
+      <c r="O51" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>153</v>
+      </c>
+      <c r="C52" t="s">
+        <v>154</v>
+      </c>
+      <c r="D52" t="s">
+        <v>155</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52" t="s">
+        <v>156</v>
+      </c>
+      <c r="G52" t="s">
+        <v>157</v>
+      </c>
+      <c r="H52" t="s">
+        <v>158</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52" t="s">
+        <v>159</v>
+      </c>
+      <c r="K52" t="s">
+        <v>121</v>
+      </c>
+      <c r="L52" t="s">
+        <v>74</v>
+      </c>
+      <c r="M52" t="s">
+        <v>160</v>
+      </c>
+      <c r="N52" t="s">
+        <v>161</v>
+      </c>
+      <c r="O52" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C53" t="s">
+        <v>163</v>
+      </c>
+      <c r="D53" t="s">
+        <v>164</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53" t="s">
+        <v>165</v>
+      </c>
+      <c r="G53" t="s">
+        <v>166</v>
+      </c>
+      <c r="H53" t="s">
+        <v>167</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53" t="s">
+        <v>168</v>
+      </c>
+      <c r="K53" t="s">
+        <v>169</v>
+      </c>
+      <c r="L53" t="s">
+        <v>170</v>
+      </c>
+      <c r="M53" t="s">
+        <v>58</v>
+      </c>
+      <c r="N53" t="s">
+        <v>171</v>
+      </c>
+      <c r="O53" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>173</v>
+      </c>
+      <c r="C54" t="s">
+        <v>174</v>
+      </c>
+      <c r="D54" t="s">
+        <v>175</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54" t="s">
+        <v>176</v>
+      </c>
+      <c r="G54" t="s">
+        <v>177</v>
+      </c>
+      <c r="H54" t="s">
+        <v>58</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54" t="s">
+        <v>178</v>
+      </c>
+      <c r="K54" t="s">
+        <v>179</v>
+      </c>
+      <c r="L54" t="s">
+        <v>74</v>
+      </c>
+      <c r="M54" t="s">
+        <v>180</v>
+      </c>
+      <c r="N54" t="s">
+        <v>181</v>
+      </c>
+      <c r="O54" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>183</v>
+      </c>
+      <c r="C55" t="s">
+        <v>184</v>
+      </c>
+      <c r="D55" t="s">
+        <v>185</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55" t="s">
+        <v>186</v>
+      </c>
+      <c r="G55" t="s">
+        <v>187</v>
+      </c>
+      <c r="H55" t="s">
+        <v>58</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55" t="s">
+        <v>188</v>
+      </c>
+      <c r="K55" t="s">
+        <v>189</v>
+      </c>
+      <c r="L55" t="s">
+        <v>190</v>
+      </c>
+      <c r="M55" t="s">
+        <v>191</v>
+      </c>
+      <c r="N55" t="s">
+        <v>192</v>
+      </c>
+      <c r="O55" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>194</v>
+      </c>
+      <c r="C56" t="s">
+        <v>195</v>
+      </c>
+      <c r="D56" t="s">
+        <v>58</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56" t="s">
+        <v>196</v>
+      </c>
+      <c r="G56" t="s">
+        <v>197</v>
+      </c>
+      <c r="H56" t="s">
+        <v>58</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56" t="s">
+        <v>198</v>
+      </c>
+      <c r="K56" t="s">
+        <v>199</v>
+      </c>
+      <c r="L56" t="s">
+        <v>200</v>
+      </c>
+      <c r="M56" t="s">
+        <v>201</v>
+      </c>
+      <c r="N56" t="s">
+        <v>202</v>
+      </c>
+      <c r="O56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>203</v>
+      </c>
+      <c r="C57" t="s">
+        <v>204</v>
+      </c>
+      <c r="D57" t="s">
+        <v>88</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57" t="s">
+        <v>205</v>
+      </c>
+      <c r="G57" t="s">
+        <v>206</v>
+      </c>
+      <c r="H57" t="s">
+        <v>58</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57" t="s">
+        <v>207</v>
+      </c>
+      <c r="K57" t="s">
+        <v>208</v>
+      </c>
+      <c r="L57" t="s">
+        <v>209</v>
+      </c>
+      <c r="M57" t="s">
+        <v>210</v>
+      </c>
+      <c r="N57" t="s">
+        <v>211</v>
+      </c>
+      <c r="O57" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>212</v>
+      </c>
+      <c r="C58" t="s">
+        <v>213</v>
+      </c>
+      <c r="D58" t="s">
+        <v>214</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58" t="s">
+        <v>215</v>
+      </c>
+      <c r="G58" t="s">
+        <v>216</v>
+      </c>
+      <c r="H58" t="s">
+        <v>217</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58" t="s">
+        <v>218</v>
+      </c>
+      <c r="K58" t="s">
+        <v>219</v>
+      </c>
+      <c r="L58" t="s">
+        <v>220</v>
+      </c>
+      <c r="M58" t="s">
+        <v>221</v>
+      </c>
+      <c r="N58" t="s">
+        <v>222</v>
+      </c>
+      <c r="O58" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>223</v>
+      </c>
+      <c r="C59" t="s">
+        <v>224</v>
+      </c>
+      <c r="D59" t="s">
+        <v>58</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59" t="s">
+        <v>225</v>
+      </c>
+      <c r="G59" t="s">
+        <v>226</v>
+      </c>
+      <c r="H59" t="s">
+        <v>227</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59" t="s">
+        <v>228</v>
+      </c>
+      <c r="K59" t="s">
+        <v>229</v>
+      </c>
+      <c r="L59" t="s">
+        <v>230</v>
+      </c>
+      <c r="M59" t="s">
+        <v>231</v>
+      </c>
+      <c r="N59" t="s">
+        <v>232</v>
+      </c>
+      <c r="O59" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>234</v>
+      </c>
+      <c r="C60" t="s">
+        <v>235</v>
+      </c>
+      <c r="D60" t="s">
+        <v>58</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60" t="s">
+        <v>236</v>
+      </c>
+      <c r="G60" t="s">
+        <v>237</v>
+      </c>
+      <c r="H60" t="s">
+        <v>186</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60" t="s">
+        <v>238</v>
+      </c>
+      <c r="K60" t="s">
+        <v>239</v>
+      </c>
+      <c r="L60" t="s">
+        <v>74</v>
+      </c>
+      <c r="M60" t="s">
+        <v>240</v>
+      </c>
+      <c r="N60" t="s">
+        <v>241</v>
+      </c>
+      <c r="O60" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>242</v>
+      </c>
+      <c r="C61" t="s">
+        <v>107</v>
+      </c>
+      <c r="D61" t="s">
+        <v>243</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61" t="s">
+        <v>244</v>
+      </c>
+      <c r="G61" t="s">
+        <v>245</v>
+      </c>
+      <c r="H61" t="s">
+        <v>246</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61" t="s">
+        <v>247</v>
+      </c>
+      <c r="K61" t="s">
+        <v>57</v>
+      </c>
+      <c r="L61" t="s">
+        <v>74</v>
+      </c>
+      <c r="M61" t="s">
+        <v>248</v>
+      </c>
+      <c r="N61" t="s">
+        <v>249</v>
+      </c>
+      <c r="O61" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>251</v>
+      </c>
+      <c r="C62" t="s">
+        <v>107</v>
+      </c>
+      <c r="D62" t="s">
+        <v>58</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62" t="s">
+        <v>252</v>
+      </c>
+      <c r="G62" t="s">
+        <v>253</v>
+      </c>
+      <c r="H62" t="s">
+        <v>254</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62" t="s">
+        <v>120</v>
+      </c>
+      <c r="K62" t="s">
+        <v>255</v>
+      </c>
+      <c r="L62" t="s">
+        <v>74</v>
+      </c>
+      <c r="M62" t="s">
+        <v>58</v>
+      </c>
+      <c r="N62" t="s">
+        <v>256</v>
+      </c>
+      <c r="O62" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>258</v>
+      </c>
+      <c r="C63" t="s">
+        <v>259</v>
+      </c>
+      <c r="D63" t="s">
+        <v>260</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63" t="s">
+        <v>261</v>
+      </c>
+      <c r="G63" t="s">
+        <v>262</v>
+      </c>
+      <c r="H63" t="s">
+        <v>263</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63" t="s">
+        <v>264</v>
+      </c>
+      <c r="K63" t="s">
+        <v>265</v>
+      </c>
+      <c r="L63" t="s">
+        <v>74</v>
+      </c>
+      <c r="M63" t="s">
+        <v>266</v>
+      </c>
+      <c r="N63" t="s">
+        <v>267</v>
+      </c>
+      <c r="O63" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>269</v>
+      </c>
+      <c r="C64" t="s">
+        <v>270</v>
+      </c>
+      <c r="D64" t="s">
+        <v>271</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64" t="s">
+        <v>272</v>
+      </c>
+      <c r="G64" t="s">
+        <v>273</v>
+      </c>
+      <c r="H64" t="s">
+        <v>58</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64" t="s">
+        <v>274</v>
+      </c>
+      <c r="K64" t="s">
+        <v>275</v>
+      </c>
+      <c r="L64" t="s">
+        <v>276</v>
+      </c>
+      <c r="M64" t="s">
+        <v>58</v>
+      </c>
+      <c r="N64" t="s">
+        <v>277</v>
+      </c>
+      <c r="O64" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>278</v>
+      </c>
+      <c r="C65" t="s">
+        <v>107</v>
+      </c>
+      <c r="D65" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65" t="s">
+        <v>279</v>
+      </c>
+      <c r="G65" t="s">
+        <v>280</v>
+      </c>
+      <c r="H65" t="s">
+        <v>58</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65" t="s">
+        <v>281</v>
+      </c>
+      <c r="K65" t="s">
+        <v>282</v>
+      </c>
+      <c r="L65" t="s">
+        <v>74</v>
+      </c>
+      <c r="M65" t="s">
+        <v>283</v>
+      </c>
+      <c r="N65" t="s">
+        <v>284</v>
+      </c>
+      <c r="O65" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>286</v>
+      </c>
+      <c r="C66" t="s">
+        <v>287</v>
+      </c>
+      <c r="D66" t="s">
+        <v>58</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66" t="s">
+        <v>288</v>
+      </c>
+      <c r="G66" t="s">
+        <v>289</v>
+      </c>
+      <c r="H66" t="s">
+        <v>290</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66" t="s">
+        <v>291</v>
+      </c>
+      <c r="K66" t="s">
+        <v>292</v>
+      </c>
+      <c r="L66" t="s">
+        <v>74</v>
+      </c>
+      <c r="M66" t="s">
+        <v>293</v>
+      </c>
+      <c r="N66" t="s">
+        <v>294</v>
+      </c>
+      <c r="O66" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>296</v>
+      </c>
+      <c r="C67" t="s">
+        <v>297</v>
+      </c>
+      <c r="D67" t="s">
+        <v>298</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67" t="s">
+        <v>299</v>
+      </c>
+      <c r="G67" t="s">
+        <v>103</v>
+      </c>
+      <c r="H67" t="s">
+        <v>300</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67" t="s">
+        <v>301</v>
+      </c>
+      <c r="K67" t="s">
+        <v>302</v>
+      </c>
+      <c r="L67" t="s">
+        <v>303</v>
+      </c>
+      <c r="M67" t="s">
+        <v>58</v>
+      </c>
+      <c r="N67" t="s">
+        <v>304</v>
+      </c>
+      <c r="O67" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>306</v>
+      </c>
+      <c r="C68" t="s">
+        <v>307</v>
+      </c>
+      <c r="D68" t="s">
+        <v>308</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68" t="s">
+        <v>309</v>
+      </c>
+      <c r="G68" t="s">
+        <v>310</v>
+      </c>
+      <c r="H68" t="s">
+        <v>311</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68" t="s">
+        <v>312</v>
+      </c>
+      <c r="K68" t="s">
+        <v>313</v>
+      </c>
+      <c r="L68" t="s">
+        <v>314</v>
+      </c>
+      <c r="M68" t="s">
+        <v>315</v>
+      </c>
+      <c r="N68" t="s">
+        <v>316</v>
+      </c>
+      <c r="O68" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>317</v>
+      </c>
+      <c r="C69" t="s">
+        <v>318</v>
+      </c>
+      <c r="D69" t="s">
+        <v>319</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69" t="s">
+        <v>320</v>
+      </c>
+      <c r="G69" t="s">
+        <v>321</v>
+      </c>
+      <c r="H69" t="s">
+        <v>58</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69" t="s">
+        <v>322</v>
+      </c>
+      <c r="K69" t="s">
+        <v>323</v>
+      </c>
+      <c r="L69" t="s">
+        <v>324</v>
+      </c>
+      <c r="M69" t="s">
+        <v>325</v>
+      </c>
+      <c r="N69" t="s">
+        <v>326</v>
+      </c>
+      <c r="O69" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>328</v>
+      </c>
+      <c r="C70" t="s">
+        <v>329</v>
+      </c>
+      <c r="D70" t="s">
+        <v>209</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70" t="s">
+        <v>330</v>
+      </c>
+      <c r="G70" t="s">
+        <v>331</v>
+      </c>
+      <c r="H70" t="s">
+        <v>59</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70" t="s">
+        <v>332</v>
+      </c>
+      <c r="K70" t="s">
+        <v>333</v>
+      </c>
+      <c r="L70" t="s">
+        <v>334</v>
+      </c>
+      <c r="M70" t="s">
+        <v>335</v>
+      </c>
+      <c r="N70" t="s">
+        <v>336</v>
+      </c>
+      <c r="O70" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>338</v>
+      </c>
+      <c r="C71" t="s">
+        <v>339</v>
+      </c>
+      <c r="D71" t="s">
+        <v>340</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71" t="s">
+        <v>341</v>
+      </c>
+      <c r="G71" t="s">
+        <v>342</v>
+      </c>
+      <c r="H71" t="s">
+        <v>343</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71" t="s">
+        <v>344</v>
+      </c>
+      <c r="K71" t="s">
+        <v>345</v>
+      </c>
+      <c r="L71" t="s">
+        <v>346</v>
+      </c>
+      <c r="M71" t="s">
+        <v>347</v>
+      </c>
+      <c r="N71" t="s">
+        <v>348</v>
+      </c>
+      <c r="O71" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>349</v>
+      </c>
+      <c r="C72" t="s">
+        <v>350</v>
+      </c>
+      <c r="D72" t="s">
+        <v>58</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72" t="s">
+        <v>351</v>
+      </c>
+      <c r="G72" t="s">
+        <v>352</v>
+      </c>
+      <c r="H72" t="s">
+        <v>353</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72" t="s">
+        <v>354</v>
+      </c>
+      <c r="K72" t="s">
+        <v>355</v>
+      </c>
+      <c r="L72" t="s">
+        <v>356</v>
+      </c>
+      <c r="M72" t="s">
+        <v>357</v>
+      </c>
+      <c r="N72" t="s">
+        <v>358</v>
+      </c>
+      <c r="O72" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>360</v>
+      </c>
+      <c r="C73" t="s">
+        <v>361</v>
+      </c>
+      <c r="D73" t="s">
+        <v>69</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73" t="s">
+        <v>362</v>
+      </c>
+      <c r="G73" t="s">
+        <v>363</v>
+      </c>
+      <c r="H73" t="s">
+        <v>364</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73" t="s">
+        <v>365</v>
+      </c>
+      <c r="K73" t="s">
+        <v>366</v>
+      </c>
+      <c r="L73" t="s">
+        <v>74</v>
+      </c>
+      <c r="M73" t="s">
+        <v>367</v>
+      </c>
+      <c r="N73" t="s">
+        <v>368</v>
+      </c>
+      <c r="O73" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>369</v>
+      </c>
+      <c r="C74" t="s">
+        <v>107</v>
+      </c>
+      <c r="D74" t="s">
+        <v>370</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74" t="s">
+        <v>371</v>
+      </c>
+      <c r="G74" t="s">
+        <v>372</v>
+      </c>
+      <c r="H74" t="s">
+        <v>373</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74" t="s">
+        <v>374</v>
+      </c>
+      <c r="K74" t="s">
+        <v>102</v>
+      </c>
+      <c r="L74" t="s">
+        <v>74</v>
+      </c>
+      <c r="M74" t="s">
+        <v>375</v>
+      </c>
+      <c r="N74" t="s">
+        <v>376</v>
+      </c>
+      <c r="O74" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>378</v>
+      </c>
+      <c r="C75" t="s">
+        <v>379</v>
+      </c>
+      <c r="D75" t="s">
+        <v>380</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75" t="s">
+        <v>381</v>
+      </c>
+      <c r="G75" t="s">
+        <v>334</v>
+      </c>
+      <c r="H75" t="s">
+        <v>382</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75" t="s">
+        <v>383</v>
+      </c>
+      <c r="K75" t="s">
+        <v>384</v>
+      </c>
+      <c r="L75" t="s">
+        <v>334</v>
+      </c>
+      <c r="M75" t="s">
+        <v>385</v>
+      </c>
+      <c r="N75" t="s">
+        <v>386</v>
+      </c>
+      <c r="O75" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>387</v>
+      </c>
+      <c r="C76" t="s">
+        <v>107</v>
+      </c>
+      <c r="D76" t="s">
+        <v>58</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76" t="s">
+        <v>388</v>
+      </c>
+      <c r="G76" t="s">
+        <v>389</v>
+      </c>
+      <c r="H76" t="s">
+        <v>167</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76" t="s">
+        <v>390</v>
+      </c>
+      <c r="K76" t="s">
+        <v>391</v>
+      </c>
+      <c r="L76" t="s">
+        <v>74</v>
+      </c>
+      <c r="M76" t="s">
+        <v>58</v>
+      </c>
+      <c r="N76" t="s">
+        <v>392</v>
+      </c>
+      <c r="O76" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>394</v>
+      </c>
+      <c r="C77" t="s">
+        <v>395</v>
+      </c>
+      <c r="D77" t="s">
+        <v>396</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77" t="s">
+        <v>397</v>
+      </c>
+      <c r="G77" t="s">
+        <v>398</v>
+      </c>
+      <c r="H77" t="s">
+        <v>58</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77" t="s">
+        <v>399</v>
+      </c>
+      <c r="K77" t="s">
+        <v>74</v>
+      </c>
+      <c r="L77" t="s">
+        <v>74</v>
+      </c>
+      <c r="M77" t="s">
+        <v>400</v>
+      </c>
+      <c r="N77" t="s">
+        <v>401</v>
+      </c>
+      <c r="O77" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>403</v>
+      </c>
+      <c r="C78" t="s">
+        <v>404</v>
+      </c>
+      <c r="D78" t="s">
+        <v>303</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78" t="s">
+        <v>405</v>
+      </c>
+      <c r="G78" t="s">
+        <v>406</v>
+      </c>
+      <c r="H78" t="s">
+        <v>58</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78" t="s">
+        <v>407</v>
+      </c>
+      <c r="K78" t="s">
+        <v>408</v>
+      </c>
+      <c r="L78" t="s">
+        <v>409</v>
+      </c>
+      <c r="M78" t="s">
+        <v>410</v>
+      </c>
+      <c r="N78" t="s">
+        <v>411</v>
+      </c>
+      <c r="O78" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>413</v>
+      </c>
+      <c r="C79" t="s">
+        <v>414</v>
+      </c>
+      <c r="D79" t="s">
+        <v>415</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79" t="s">
+        <v>416</v>
+      </c>
+      <c r="G79" t="s">
+        <v>417</v>
+      </c>
+      <c r="H79" t="s">
+        <v>58</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79" t="s">
+        <v>418</v>
+      </c>
+      <c r="K79" t="s">
+        <v>158</v>
+      </c>
+      <c r="L79" t="s">
+        <v>156</v>
+      </c>
+      <c r="M79" t="s">
+        <v>58</v>
+      </c>
+      <c r="N79" t="s">
+        <v>419</v>
+      </c>
+      <c r="O79" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>421</v>
+      </c>
+      <c r="C80" t="s">
+        <v>107</v>
+      </c>
+      <c r="D80" t="s">
+        <v>422</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80" t="s">
+        <v>423</v>
+      </c>
+      <c r="G80" t="s">
+        <v>424</v>
+      </c>
+      <c r="H80" t="s">
+        <v>425</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80" t="s">
+        <v>426</v>
+      </c>
+      <c r="K80" t="s">
+        <v>427</v>
+      </c>
+      <c r="L80" t="s">
+        <v>428</v>
+      </c>
+      <c r="M80" t="s">
+        <v>58</v>
+      </c>
+      <c r="N80" t="s">
+        <v>429</v>
+      </c>
+      <c r="O80" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>430</v>
+      </c>
+      <c r="C81" t="s">
+        <v>431</v>
+      </c>
+      <c r="D81" t="s">
+        <v>58</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81" t="s">
+        <v>432</v>
+      </c>
+      <c r="G81" t="s">
+        <v>433</v>
+      </c>
+      <c r="H81" t="s">
+        <v>434</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81" t="s">
+        <v>120</v>
+      </c>
+      <c r="K81" t="s">
+        <v>435</v>
+      </c>
+      <c r="L81" t="s">
+        <v>436</v>
+      </c>
+      <c r="M81" t="s">
+        <v>58</v>
+      </c>
+      <c r="N81" t="s">
+        <v>437</v>
+      </c>
+      <c r="O81" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>439</v>
+      </c>
+      <c r="C82" t="s">
+        <v>440</v>
+      </c>
+      <c r="D82" t="s">
+        <v>441</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82" t="s">
+        <v>442</v>
+      </c>
+      <c r="G82" t="s">
+        <v>443</v>
+      </c>
+      <c r="H82" t="s">
+        <v>58</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82" t="s">
+        <v>444</v>
+      </c>
+      <c r="K82" t="s">
+        <v>445</v>
+      </c>
+      <c r="L82" t="s">
+        <v>74</v>
+      </c>
+      <c r="M82" t="s">
+        <v>58</v>
+      </c>
+      <c r="N82" t="s">
+        <v>446</v>
+      </c>
+      <c r="O82" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>448</v>
+      </c>
+      <c r="C83" t="s">
+        <v>107</v>
+      </c>
+      <c r="D83" t="s">
+        <v>58</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83" t="s">
+        <v>449</v>
+      </c>
+      <c r="G83" t="s">
+        <v>450</v>
+      </c>
+      <c r="H83" t="s">
+        <v>58</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83" t="s">
+        <v>451</v>
+      </c>
+      <c r="K83" t="s">
+        <v>108</v>
+      </c>
+      <c r="L83" t="s">
+        <v>74</v>
+      </c>
+      <c r="M83" t="s">
+        <v>58</v>
+      </c>
+      <c r="N83" t="s">
+        <v>452</v>
+      </c>
+      <c r="O83" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>454</v>
+      </c>
+      <c r="C84" t="s">
+        <v>455</v>
+      </c>
+      <c r="D84" t="s">
+        <v>456</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84" t="s">
+        <v>457</v>
+      </c>
+      <c r="G84" t="s">
+        <v>255</v>
+      </c>
+      <c r="H84" t="s">
+        <v>458</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84" t="s">
+        <v>459</v>
+      </c>
+      <c r="K84" t="s">
+        <v>460</v>
+      </c>
+      <c r="L84" t="s">
+        <v>74</v>
+      </c>
+      <c r="M84" t="s">
+        <v>461</v>
+      </c>
+      <c r="N84" t="s">
+        <v>462</v>
+      </c>
+      <c r="O84" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>464</v>
+      </c>
+      <c r="C85" t="s">
+        <v>107</v>
+      </c>
+      <c r="D85" t="s">
+        <v>465</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85" t="s">
+        <v>466</v>
+      </c>
+      <c r="G85" t="s">
+        <v>467</v>
+      </c>
+      <c r="H85" t="s">
+        <v>468</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85" t="s">
+        <v>120</v>
+      </c>
+      <c r="K85" t="s">
+        <v>425</v>
+      </c>
+      <c r="L85" t="s">
+        <v>469</v>
+      </c>
+      <c r="M85" t="s">
+        <v>58</v>
+      </c>
+      <c r="N85" t="s">
+        <v>470</v>
+      </c>
+      <c r="O85" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>472</v>
+      </c>
+      <c r="C86" t="s">
+        <v>473</v>
+      </c>
+      <c r="D86" t="s">
+        <v>58</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86" t="s">
+        <v>474</v>
+      </c>
+      <c r="G86" t="s">
+        <v>475</v>
+      </c>
+      <c r="H86" t="s">
+        <v>476</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86" t="s">
+        <v>477</v>
+      </c>
+      <c r="K86" t="s">
+        <v>478</v>
+      </c>
+      <c r="L86" t="s">
+        <v>461</v>
+      </c>
+      <c r="M86" t="s">
+        <v>479</v>
+      </c>
+      <c r="N86" t="s">
+        <v>480</v>
+      </c>
+      <c r="O86" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>481</v>
+      </c>
+      <c r="C87" t="s">
+        <v>482</v>
+      </c>
+      <c r="D87" t="s">
+        <v>58</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87" t="s">
+        <v>139</v>
+      </c>
+      <c r="G87" t="s">
+        <v>483</v>
+      </c>
+      <c r="H87" t="s">
+        <v>58</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87" t="s">
+        <v>484</v>
+      </c>
+      <c r="K87" t="s">
+        <v>465</v>
+      </c>
+      <c r="L87" t="s">
+        <v>74</v>
+      </c>
+      <c r="M87" t="s">
+        <v>485</v>
+      </c>
+      <c r="N87" t="s">
+        <v>486</v>
+      </c>
+      <c r="O87" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>488</v>
+      </c>
+      <c r="C88" t="s">
+        <v>489</v>
+      </c>
+      <c r="D88" t="s">
+        <v>58</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88" t="s">
+        <v>490</v>
+      </c>
+      <c r="G88" t="s">
+        <v>491</v>
+      </c>
+      <c r="H88" t="s">
+        <v>492</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88" t="s">
+        <v>493</v>
+      </c>
+      <c r="K88" t="s">
+        <v>494</v>
+      </c>
+      <c r="L88" t="s">
+        <v>74</v>
+      </c>
+      <c r="M88" t="s">
+        <v>58</v>
+      </c>
+      <c r="N88" t="s">
+        <v>495</v>
+      </c>
+      <c r="O88" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>496</v>
+      </c>
+      <c r="C89" t="s">
+        <v>497</v>
+      </c>
+      <c r="D89" t="s">
+        <v>340</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89" t="s">
+        <v>498</v>
+      </c>
+      <c r="G89" t="s">
+        <v>499</v>
+      </c>
+      <c r="H89" t="s">
+        <v>500</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89" t="s">
+        <v>501</v>
+      </c>
+      <c r="K89" t="s">
+        <v>502</v>
+      </c>
+      <c r="L89" t="s">
+        <v>74</v>
+      </c>
+      <c r="M89" t="s">
+        <v>58</v>
+      </c>
+      <c r="N89" t="s">
+        <v>503</v>
+      </c>
+      <c r="O89" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>505</v>
+      </c>
+      <c r="C90" t="s">
+        <v>506</v>
+      </c>
+      <c r="D90" t="s">
+        <v>58</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90" t="s">
+        <v>507</v>
+      </c>
+      <c r="G90" t="s">
+        <v>508</v>
+      </c>
+      <c r="H90" t="s">
+        <v>509</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90" t="s">
+        <v>510</v>
+      </c>
+      <c r="K90" t="s">
+        <v>511</v>
+      </c>
+      <c r="L90" t="s">
+        <v>409</v>
+      </c>
+      <c r="M90" t="s">
+        <v>58</v>
+      </c>
+      <c r="N90" t="s">
+        <v>512</v>
+      </c>
+      <c r="O90" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>513</v>
+      </c>
+      <c r="C91" t="s">
+        <v>514</v>
+      </c>
+      <c r="D91" t="s">
+        <v>515</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91" t="s">
+        <v>516</v>
+      </c>
+      <c r="G91" t="s">
+        <v>314</v>
+      </c>
+      <c r="H91" t="s">
+        <v>517</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91" t="s">
+        <v>518</v>
+      </c>
+      <c r="K91" t="s">
+        <v>519</v>
+      </c>
+      <c r="L91" t="s">
+        <v>520</v>
+      </c>
+      <c r="M91" t="s">
+        <v>521</v>
+      </c>
+      <c r="N91" t="s">
+        <v>522</v>
+      </c>
+      <c r="O91" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>524</v>
+      </c>
+      <c r="C92" t="s">
+        <v>525</v>
+      </c>
+      <c r="D92" t="s">
+        <v>526</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92" t="s">
+        <v>527</v>
+      </c>
+      <c r="G92" t="s">
+        <v>441</v>
+      </c>
+      <c r="H92" t="s">
+        <v>528</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92" t="s">
+        <v>529</v>
+      </c>
+      <c r="K92" t="s">
+        <v>530</v>
+      </c>
+      <c r="L92" t="s">
+        <v>531</v>
+      </c>
+      <c r="M92" t="s">
+        <v>532</v>
+      </c>
+      <c r="N92" t="s">
+        <v>533</v>
+      </c>
+      <c r="O92" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>535</v>
+      </c>
+      <c r="C93" t="s">
+        <v>107</v>
+      </c>
+      <c r="D93" t="s">
+        <v>536</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93" t="s">
+        <v>537</v>
+      </c>
+      <c r="G93" t="s">
+        <v>538</v>
+      </c>
+      <c r="H93" t="s">
+        <v>539</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93" t="s">
+        <v>540</v>
+      </c>
+      <c r="K93" t="s">
+        <v>541</v>
+      </c>
+      <c r="L93" t="s">
+        <v>74</v>
+      </c>
+      <c r="M93" t="s">
+        <v>542</v>
+      </c>
+      <c r="N93" t="s">
+        <v>543</v>
+      </c>
+      <c r="O93" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>544</v>
+      </c>
+      <c r="C94" t="s">
+        <v>545</v>
+      </c>
+      <c r="D94" t="s">
+        <v>546</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94" t="s">
+        <v>547</v>
+      </c>
+      <c r="G94" t="s">
+        <v>548</v>
+      </c>
+      <c r="H94" t="s">
+        <v>549</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94" t="s">
+        <v>550</v>
+      </c>
+      <c r="K94" t="s">
+        <v>551</v>
+      </c>
+      <c r="L94" t="s">
+        <v>552</v>
+      </c>
+      <c r="M94" t="s">
+        <v>553</v>
+      </c>
+      <c r="N94" t="s">
+        <v>554</v>
+      </c>
+      <c r="O94" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>555</v>
+      </c>
+      <c r="C95" t="s">
+        <v>107</v>
+      </c>
+      <c r="D95" t="s">
+        <v>156</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95" t="s">
+        <v>137</v>
+      </c>
+      <c r="G95" t="s">
+        <v>556</v>
+      </c>
+      <c r="H95" t="s">
+        <v>58</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95" t="s">
+        <v>557</v>
+      </c>
+      <c r="K95" t="s">
+        <v>558</v>
+      </c>
+      <c r="L95" t="s">
+        <v>179</v>
+      </c>
+      <c r="M95" t="s">
+        <v>58</v>
+      </c>
+      <c r="N95" t="s">
+        <v>559</v>
+      </c>
+      <c r="O95" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>561</v>
+      </c>
+      <c r="C96" t="s">
+        <v>107</v>
+      </c>
+      <c r="D96" t="s">
+        <v>562</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96" t="s">
+        <v>563</v>
+      </c>
+      <c r="G96" t="s">
+        <v>564</v>
+      </c>
+      <c r="H96" t="s">
+        <v>502</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96" t="s">
+        <v>405</v>
+      </c>
+      <c r="K96" t="s">
+        <v>57</v>
+      </c>
+      <c r="L96" t="s">
+        <v>74</v>
+      </c>
+      <c r="M96" t="s">
+        <v>565</v>
+      </c>
+      <c r="N96" t="s">
+        <v>566</v>
+      </c>
+      <c r="O96" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>568</v>
+      </c>
+      <c r="C97" t="s">
+        <v>107</v>
+      </c>
+      <c r="D97" t="s">
+        <v>58</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97" t="s">
+        <v>569</v>
+      </c>
+      <c r="G97" t="s">
+        <v>570</v>
+      </c>
+      <c r="H97" t="s">
+        <v>571</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97" t="s">
+        <v>572</v>
+      </c>
+      <c r="K97" t="s">
+        <v>573</v>
+      </c>
+      <c r="L97" t="s">
+        <v>574</v>
+      </c>
+      <c r="M97" t="s">
+        <v>58</v>
+      </c>
+      <c r="N97" t="s">
+        <v>575</v>
+      </c>
+      <c r="O97" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>577</v>
+      </c>
+      <c r="C98" t="s">
+        <v>578</v>
+      </c>
+      <c r="D98" t="s">
+        <v>579</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98" t="s">
+        <v>580</v>
+      </c>
+      <c r="G98" t="s">
+        <v>334</v>
+      </c>
+      <c r="H98" t="s">
+        <v>58</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98" t="s">
+        <v>581</v>
+      </c>
+      <c r="K98" t="s">
+        <v>248</v>
+      </c>
+      <c r="L98" t="s">
+        <v>582</v>
+      </c>
+      <c r="M98" t="s">
+        <v>583</v>
+      </c>
+      <c r="N98" t="s">
+        <v>584</v>
+      </c>
+      <c r="O98" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>586</v>
+      </c>
+      <c r="C99" t="s">
+        <v>587</v>
+      </c>
+      <c r="D99" t="s">
+        <v>588</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99" t="s">
+        <v>589</v>
+      </c>
+      <c r="G99" t="s">
+        <v>79</v>
+      </c>
+      <c r="H99" t="s">
+        <v>590</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99" t="s">
+        <v>591</v>
+      </c>
+      <c r="K99" t="s">
+        <v>592</v>
+      </c>
+      <c r="L99" t="s">
+        <v>74</v>
+      </c>
+      <c r="M99" t="s">
+        <v>58</v>
+      </c>
+      <c r="N99" t="s">
+        <v>593</v>
+      </c>
+      <c r="O99" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>595</v>
+      </c>
+      <c r="C100" t="s">
+        <v>596</v>
+      </c>
+      <c r="D100" t="s">
+        <v>58</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100" t="s">
+        <v>597</v>
+      </c>
+      <c r="G100" t="s">
+        <v>598</v>
+      </c>
+      <c r="H100" t="s">
+        <v>599</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100" t="s">
+        <v>600</v>
+      </c>
+      <c r="K100" t="s">
+        <v>601</v>
+      </c>
+      <c r="L100" t="s">
+        <v>410</v>
+      </c>
+      <c r="M100" t="s">
+        <v>58</v>
+      </c>
+      <c r="N100" t="s">
+        <v>602</v>
+      </c>
+      <c r="O100" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>604</v>
+      </c>
+      <c r="C101" t="s">
+        <v>107</v>
+      </c>
+      <c r="D101" t="s">
+        <v>605</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101" t="s">
+        <v>606</v>
+      </c>
+      <c r="G101" t="s">
+        <v>433</v>
+      </c>
+      <c r="H101" t="s">
+        <v>58</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101" t="s">
+        <v>120</v>
+      </c>
+      <c r="K101" t="s">
+        <v>607</v>
+      </c>
+      <c r="L101" t="s">
+        <v>282</v>
+      </c>
+      <c r="M101" t="s">
+        <v>608</v>
+      </c>
+      <c r="N101" t="s">
+        <v>609</v>
+      </c>
+      <c r="O101" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>611</v>
+      </c>
+      <c r="C102" t="s">
+        <v>612</v>
+      </c>
+      <c r="D102" t="s">
+        <v>613</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102" t="s">
+        <v>614</v>
+      </c>
+      <c r="G102" t="s">
+        <v>615</v>
+      </c>
+      <c r="H102" t="s">
+        <v>58</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102" t="s">
+        <v>616</v>
+      </c>
+      <c r="K102" t="s">
+        <v>617</v>
+      </c>
+      <c r="L102" t="s">
+        <v>618</v>
+      </c>
+      <c r="M102" t="s">
+        <v>58</v>
+      </c>
+      <c r="N102" t="s">
+        <v>619</v>
+      </c>
+      <c r="O102" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>620</v>
+      </c>
+      <c r="C103" t="s">
+        <v>621</v>
+      </c>
+      <c r="D103" t="s">
+        <v>622</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103" t="s">
+        <v>623</v>
+      </c>
+      <c r="G103" t="s">
+        <v>624</v>
+      </c>
+      <c r="H103" t="s">
+        <v>58</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103" t="s">
+        <v>625</v>
+      </c>
+      <c r="K103" t="s">
+        <v>626</v>
+      </c>
+      <c r="L103" t="s">
+        <v>627</v>
+      </c>
+      <c r="M103" t="s">
+        <v>628</v>
+      </c>
+      <c r="N103" t="s">
+        <v>629</v>
+      </c>
+      <c r="O103" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>631</v>
+      </c>
+      <c r="C104" t="s">
+        <v>632</v>
+      </c>
+      <c r="D104" t="s">
+        <v>61</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104" t="s">
+        <v>633</v>
+      </c>
+      <c r="G104" t="s">
+        <v>417</v>
+      </c>
+      <c r="H104" t="s">
+        <v>634</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104" t="s">
+        <v>635</v>
+      </c>
+      <c r="K104" t="s">
+        <v>546</v>
+      </c>
+      <c r="L104" t="s">
+        <v>636</v>
+      </c>
+      <c r="M104" t="s">
+        <v>637</v>
+      </c>
+      <c r="N104" t="s">
+        <v>638</v>
+      </c>
+      <c r="O104" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>640</v>
+      </c>
+      <c r="C105" t="s">
+        <v>107</v>
+      </c>
+      <c r="D105" t="s">
+        <v>308</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105" t="s">
+        <v>108</v>
+      </c>
+      <c r="G105" t="s">
+        <v>641</v>
+      </c>
+      <c r="H105" t="s">
+        <v>58</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105" t="s">
+        <v>642</v>
+      </c>
+      <c r="K105" t="s">
+        <v>112</v>
+      </c>
+      <c r="L105" t="s">
+        <v>74</v>
+      </c>
+      <c r="M105" t="s">
+        <v>643</v>
+      </c>
+      <c r="N105" t="s">
+        <v>644</v>
+      </c>
+      <c r="O105" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>646</v>
+      </c>
+      <c r="C106" t="s">
+        <v>647</v>
+      </c>
+      <c r="D106" t="s">
+        <v>200</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106" t="s">
+        <v>648</v>
+      </c>
+      <c r="G106" t="s">
+        <v>649</v>
+      </c>
+      <c r="H106" t="s">
+        <v>58</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106" t="s">
+        <v>120</v>
+      </c>
+      <c r="K106" t="s">
+        <v>650</v>
+      </c>
+      <c r="L106" t="s">
+        <v>546</v>
+      </c>
+      <c r="M106" t="s">
+        <v>58</v>
+      </c>
+      <c r="N106" t="s">
+        <v>293</v>
+      </c>
+      <c r="O106" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>652</v>
+      </c>
+      <c r="C107" t="s">
+        <v>107</v>
+      </c>
+      <c r="D107" t="s">
+        <v>653</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107" t="s">
+        <v>654</v>
+      </c>
+      <c r="G107" t="s">
+        <v>655</v>
+      </c>
+      <c r="H107" t="s">
+        <v>656</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107" t="s">
+        <v>657</v>
+      </c>
+      <c r="K107" t="s">
+        <v>658</v>
+      </c>
+      <c r="L107" t="s">
+        <v>74</v>
+      </c>
+      <c r="M107" t="s">
+        <v>659</v>
+      </c>
+      <c r="N107" t="s">
+        <v>660</v>
+      </c>
+      <c r="O107" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>662</v>
+      </c>
+      <c r="C108" t="s">
+        <v>663</v>
+      </c>
+      <c r="D108" t="s">
+        <v>396</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108" t="s">
+        <v>664</v>
+      </c>
+      <c r="G108" t="s">
+        <v>665</v>
+      </c>
+      <c r="H108" t="s">
+        <v>666</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108" t="s">
+        <v>667</v>
+      </c>
+      <c r="K108" t="s">
+        <v>668</v>
+      </c>
+      <c r="L108" t="s">
+        <v>74</v>
+      </c>
+      <c r="M108" t="s">
+        <v>669</v>
+      </c>
+      <c r="N108" t="s">
+        <v>670</v>
+      </c>
+      <c r="O108" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>672</v>
+      </c>
+      <c r="C109" t="s">
+        <v>107</v>
+      </c>
+      <c r="D109" t="s">
+        <v>673</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109" t="s">
+        <v>590</v>
+      </c>
+      <c r="G109" t="s">
+        <v>674</v>
+      </c>
+      <c r="H109" t="s">
+        <v>58</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109" t="s">
+        <v>675</v>
+      </c>
+      <c r="K109" t="s">
+        <v>676</v>
+      </c>
+      <c r="L109" t="s">
+        <v>677</v>
+      </c>
+      <c r="M109" t="s">
+        <v>58</v>
+      </c>
+      <c r="N109" t="s">
+        <v>509</v>
+      </c>
+      <c r="O109" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>679</v>
+      </c>
+      <c r="C110" t="s">
+        <v>680</v>
+      </c>
+      <c r="D110" t="s">
+        <v>58</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110" t="s">
+        <v>681</v>
+      </c>
+      <c r="G110" t="s">
+        <v>682</v>
+      </c>
+      <c r="H110" t="s">
+        <v>58</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110" t="s">
+        <v>683</v>
+      </c>
+      <c r="K110" t="s">
+        <v>684</v>
+      </c>
+      <c r="L110" t="s">
+        <v>685</v>
+      </c>
+      <c r="M110" t="s">
+        <v>686</v>
+      </c>
+      <c r="N110" t="s">
+        <v>687</v>
+      </c>
+      <c r="O110" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>689</v>
+      </c>
+      <c r="C111" t="s">
+        <v>107</v>
+      </c>
+      <c r="D111" t="s">
+        <v>58</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111" t="s">
+        <v>690</v>
+      </c>
+      <c r="G111" t="s">
+        <v>691</v>
+      </c>
+      <c r="H111" t="s">
+        <v>692</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111" t="s">
+        <v>120</v>
+      </c>
+      <c r="K111" t="s">
+        <v>693</v>
+      </c>
+      <c r="L111" t="s">
+        <v>370</v>
+      </c>
+      <c r="M111" t="s">
+        <v>694</v>
+      </c>
+      <c r="N111" t="s">
+        <v>695</v>
+      </c>
+      <c r="O111" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>696</v>
+      </c>
+      <c r="C112" t="s">
+        <v>107</v>
+      </c>
+      <c r="D112" t="s">
+        <v>58</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112" t="s">
+        <v>697</v>
+      </c>
+      <c r="G112" t="s">
+        <v>698</v>
+      </c>
+      <c r="H112" t="s">
+        <v>699</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112" t="s">
+        <v>700</v>
+      </c>
+      <c r="K112" t="s">
+        <v>701</v>
+      </c>
+      <c r="L112" t="s">
+        <v>702</v>
+      </c>
+      <c r="M112" t="s">
+        <v>703</v>
+      </c>
+      <c r="N112" t="s">
+        <v>704</v>
+      </c>
+      <c r="O112" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>706</v>
+      </c>
+      <c r="C113" t="s">
+        <v>707</v>
+      </c>
+      <c r="D113" t="s">
+        <v>708</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113" t="s">
+        <v>709</v>
+      </c>
+      <c r="G113" t="s">
+        <v>237</v>
+      </c>
+      <c r="H113" t="s">
+        <v>710</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113" t="s">
+        <v>711</v>
+      </c>
+      <c r="K113" t="s">
+        <v>712</v>
+      </c>
+      <c r="L113" t="s">
+        <v>713</v>
+      </c>
+      <c r="M113" t="s">
+        <v>58</v>
+      </c>
+      <c r="N113" t="s">
+        <v>714</v>
+      </c>
+      <c r="O113" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>716</v>
+      </c>
+      <c r="C114" t="s">
+        <v>717</v>
+      </c>
+      <c r="D114" t="s">
+        <v>58</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114" t="s">
+        <v>718</v>
+      </c>
+      <c r="G114" t="s">
+        <v>719</v>
+      </c>
+      <c r="H114" t="s">
+        <v>720</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114" t="s">
+        <v>721</v>
+      </c>
+      <c r="K114" t="s">
+        <v>676</v>
+      </c>
+      <c r="L114" t="s">
+        <v>722</v>
+      </c>
+      <c r="M114" t="s">
+        <v>723</v>
+      </c>
+      <c r="N114" t="s">
+        <v>724</v>
+      </c>
+      <c r="O114" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>726</v>
+      </c>
+      <c r="C115" t="s">
+        <v>727</v>
+      </c>
+      <c r="D115" t="s">
+        <v>502</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115" t="s">
+        <v>108</v>
+      </c>
+      <c r="G115" t="s">
+        <v>334</v>
+      </c>
+      <c r="H115" t="s">
+        <v>58</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115" t="s">
+        <v>120</v>
+      </c>
+      <c r="K115" t="s">
+        <v>728</v>
+      </c>
+      <c r="L115" t="s">
+        <v>729</v>
+      </c>
+      <c r="M115" t="s">
+        <v>730</v>
+      </c>
+      <c r="N115" t="s">
+        <v>731</v>
+      </c>
+      <c r="O115" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>733</v>
+      </c>
+      <c r="C116" t="s">
+        <v>107</v>
+      </c>
+      <c r="D116" t="s">
+        <v>58</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116" t="s">
+        <v>734</v>
+      </c>
+      <c r="G116" t="s">
+        <v>382</v>
+      </c>
+      <c r="H116" t="s">
+        <v>735</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116" t="s">
+        <v>736</v>
+      </c>
+      <c r="K116" t="s">
+        <v>131</v>
+      </c>
+      <c r="L116" t="s">
+        <v>737</v>
+      </c>
+      <c r="M116" t="s">
+        <v>738</v>
+      </c>
+      <c r="N116" t="s">
+        <v>739</v>
+      </c>
+      <c r="O116" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>741</v>
+      </c>
+      <c r="C117" t="s">
+        <v>107</v>
+      </c>
+      <c r="D117" t="s">
+        <v>742</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117" t="s">
+        <v>743</v>
+      </c>
+      <c r="G117" t="s">
+        <v>744</v>
+      </c>
+      <c r="H117" t="s">
+        <v>745</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117" t="s">
+        <v>746</v>
+      </c>
+      <c r="K117" t="s">
+        <v>491</v>
+      </c>
+      <c r="L117" t="s">
+        <v>74</v>
+      </c>
+      <c r="M117" t="s">
+        <v>58</v>
+      </c>
+      <c r="N117" t="s">
+        <v>747</v>
+      </c>
+      <c r="O117" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>749</v>
+      </c>
+      <c r="C118" t="s">
+        <v>107</v>
+      </c>
+      <c r="D118" t="s">
+        <v>58</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118" t="s">
+        <v>750</v>
+      </c>
+      <c r="G118" t="s">
+        <v>435</v>
+      </c>
+      <c r="H118" t="s">
+        <v>751</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118" t="s">
+        <v>752</v>
+      </c>
+      <c r="K118" t="s">
+        <v>537</v>
+      </c>
+      <c r="L118" t="s">
+        <v>753</v>
+      </c>
+      <c r="M118" t="s">
+        <v>754</v>
+      </c>
+      <c r="N118" t="s">
+        <v>755</v>
+      </c>
+      <c r="O118" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>757</v>
+      </c>
+      <c r="C119" t="s">
+        <v>107</v>
+      </c>
+      <c r="D119" t="s">
+        <v>58</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119" t="s">
+        <v>758</v>
+      </c>
+      <c r="G119" t="s">
+        <v>310</v>
+      </c>
+      <c r="H119" t="s">
+        <v>58</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119" t="s">
+        <v>759</v>
+      </c>
+      <c r="K119" t="s">
+        <v>760</v>
+      </c>
+      <c r="L119" t="s">
+        <v>761</v>
+      </c>
+      <c r="M119" t="s">
+        <v>58</v>
+      </c>
+      <c r="N119" t="s">
+        <v>762</v>
+      </c>
+      <c r="O119" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>763</v>
+      </c>
+      <c r="C120" t="s">
+        <v>764</v>
+      </c>
+      <c r="D120" t="s">
+        <v>765</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120" t="s">
+        <v>766</v>
+      </c>
+      <c r="G120" t="s">
+        <v>767</v>
+      </c>
+      <c r="H120" t="s">
+        <v>768</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120" t="s">
+        <v>120</v>
+      </c>
+      <c r="K120" t="s">
+        <v>769</v>
+      </c>
+      <c r="L120" t="s">
+        <v>103</v>
+      </c>
+      <c r="M120" t="s">
+        <v>770</v>
+      </c>
+      <c r="N120" t="s">
+        <v>771</v>
+      </c>
+      <c r="O120" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>772</v>
+      </c>
+      <c r="C121" t="s">
+        <v>107</v>
+      </c>
+      <c r="D121" t="s">
+        <v>300</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121" t="s">
+        <v>773</v>
+      </c>
+      <c r="G121" t="s">
+        <v>774</v>
+      </c>
+      <c r="H121" t="s">
+        <v>58</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121" t="s">
+        <v>775</v>
+      </c>
+      <c r="K121" t="s">
+        <v>776</v>
+      </c>
+      <c r="L121" t="s">
+        <v>74</v>
+      </c>
+      <c r="M121" t="s">
+        <v>777</v>
+      </c>
+      <c r="N121" t="s">
+        <v>778</v>
+      </c>
+      <c r="O121" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>